--- a/data-source/ESTOQUEBASESLOCAL.xlsx
+++ b/data-source/ESTOQUEBASESLOCAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43BF1184-79C9-48E4-96C7-0517BAC7DE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{43BF1184-79C9-48E4-96C7-0517BAC7DE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13935F81-51DC-4872-B174-3FEF7CC5B373}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="83">
   <si>
     <t>Produto</t>
   </si>
@@ -171,12 +171,6 @@
     <t>VELVET JOLIE  PRETO LAMINADO QUADRICULADO Q072</t>
   </si>
   <si>
-    <t>NEW BASE VITORIA WZ 1.1 BLACK  (TIRAS)</t>
-  </si>
-  <si>
-    <t>NEW BASE VITORIA WZ 1.1 WHITE (TIRAS)</t>
-  </si>
-  <si>
     <t>SUEDE HOLLAND PREMIUM - 901 EUROTEXTIL - CINZA</t>
   </si>
   <si>
@@ -184,9 +178,6 @@
   </si>
   <si>
     <t>BASE SHANGHAI PU 1.05 - BEGE</t>
-  </si>
-  <si>
-    <t>NEW BASE VITORIA WZ 1.1 CREME (TIRAS)</t>
   </si>
   <si>
     <t>BASE SHANGHAI PU 1.05 - WHITE</t>
@@ -303,7 +294,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[Blue]###########0;[Red]\-###########0"/>
-    <numFmt numFmtId="166" formatCode="[Blue]###,###,###,##0.000;[Red]\-###,###,###,##0.000"/>
+    <numFmt numFmtId="165" formatCode="[Blue]###,###,###,##0.000;[Red]\-###,###,###,##0.000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -360,14 +351,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -712,7 +701,7 @@
     <col min="2" max="2" width="54.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -728,7 +717,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -745,7 +734,7 @@
       <c r="D2" s="3">
         <v>13</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -762,7 +751,7 @@
       <c r="D3" s="3">
         <v>13</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -779,8 +768,8 @@
       <c r="D4" s="3">
         <v>13</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>78</v>
+      <c r="E4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -796,8 +785,8 @@
       <c r="D5" s="3">
         <v>13</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>78</v>
+      <c r="E5" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -813,8 +802,8 @@
       <c r="D6" s="3">
         <v>13</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>79</v>
+      <c r="E6" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -830,7 +819,7 @@
       <c r="D7" s="3">
         <v>13</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" t="s">
         <v>5</v>
       </c>
     </row>
@@ -847,7 +836,7 @@
       <c r="D8" s="3">
         <v>13</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" t="s">
         <v>5</v>
       </c>
     </row>
@@ -864,8 +853,8 @@
       <c r="D9" s="3">
         <v>13</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>79</v>
+      <c r="E9" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -881,8 +870,8 @@
       <c r="D10" s="3">
         <v>13</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>80</v>
+      <c r="E10" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -898,8 +887,8 @@
       <c r="D11" s="3">
         <v>13</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>80</v>
+      <c r="E11" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -915,8 +904,8 @@
       <c r="D12" s="3">
         <v>13</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>80</v>
+      <c r="E12" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -932,8 +921,8 @@
       <c r="D13" s="3">
         <v>13</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>80</v>
+      <c r="E13" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -949,8 +938,8 @@
       <c r="D14" s="3">
         <v>13</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>80</v>
+      <c r="E14" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -966,8 +955,8 @@
       <c r="D15" s="3">
         <v>13</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>80</v>
+      <c r="E15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -983,7 +972,7 @@
       <c r="D16" s="3">
         <v>13</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1000,7 +989,7 @@
       <c r="D17" s="3">
         <v>13</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1017,7 +1006,7 @@
       <c r="D18" s="3">
         <v>13</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1034,7 +1023,7 @@
       <c r="D19" s="3">
         <v>13</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1051,7 +1040,7 @@
       <c r="D20" s="3">
         <v>13</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1068,7 +1057,7 @@
       <c r="D21" s="3">
         <v>13</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1080,13 +1069,13 @@
         <v>25</v>
       </c>
       <c r="C22" s="4">
-        <v>34462.5</v>
+        <v>32562.5</v>
       </c>
       <c r="D22" s="3">
         <v>13</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>81</v>
+      <c r="E22" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1102,8 +1091,8 @@
       <c r="D23" s="3">
         <v>13</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>82</v>
+      <c r="E23" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1119,8 +1108,8 @@
       <c r="D24" s="3">
         <v>13</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>82</v>
+      <c r="E24" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1136,7 +1125,7 @@
       <c r="D25" s="3">
         <v>13</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1153,7 +1142,7 @@
       <c r="D26" s="3">
         <v>13</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1170,7 +1159,7 @@
       <c r="D27" s="3">
         <v>13</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1187,7 +1176,7 @@
       <c r="D28" s="3">
         <v>13</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1204,7 +1193,7 @@
       <c r="D29" s="3">
         <v>13</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1221,7 +1210,7 @@
       <c r="D30" s="3">
         <v>13</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1238,7 +1227,7 @@
       <c r="D31" s="3">
         <v>13</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1255,7 +1244,7 @@
       <c r="D32" s="3">
         <v>13</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1272,7 +1261,7 @@
       <c r="D33" s="3">
         <v>13</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1289,7 +1278,7 @@
       <c r="D34" s="3">
         <v>13</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1306,8 +1295,8 @@
       <c r="D35" s="3">
         <v>13</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>80</v>
+      <c r="E35" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1323,8 +1312,8 @@
       <c r="D36" s="3">
         <v>13</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>80</v>
+      <c r="E36" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1340,8 +1329,8 @@
       <c r="D37" s="3">
         <v>13</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>80</v>
+      <c r="E37" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1357,8 +1346,8 @@
       <c r="D38" s="3">
         <v>13</v>
       </c>
-      <c r="E38" s="6" t="s">
-        <v>80</v>
+      <c r="E38" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1374,8 +1363,8 @@
       <c r="D39" s="3">
         <v>13</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>80</v>
+      <c r="E39" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1391,8 +1380,8 @@
       <c r="D40" s="3">
         <v>13</v>
       </c>
-      <c r="E40" s="6" t="s">
-        <v>80</v>
+      <c r="E40" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1408,8 +1397,8 @@
       <c r="D41" s="3">
         <v>13</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>82</v>
+      <c r="E41" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1425,7 +1414,7 @@
       <c r="D42" s="3">
         <v>13</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1442,7 +1431,7 @@
       <c r="D43" s="3">
         <v>13</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1459,8 +1448,8 @@
       <c r="D44" s="3">
         <v>13</v>
       </c>
-      <c r="E44" s="6" t="s">
-        <v>82</v>
+      <c r="E44" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1476,8 +1465,8 @@
       <c r="D45" s="3">
         <v>13</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>82</v>
+      <c r="E45" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1493,927 +1482,850 @@
       <c r="D46" s="3">
         <v>13</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <v>10568</v>
+        <v>10573</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C47" s="4">
-        <v>220</v>
+        <v>232.1</v>
       </c>
       <c r="D47" s="3">
         <v>13</v>
       </c>
-      <c r="E47" s="6" t="e">
-        <v>#N/A</v>
+      <c r="E47" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <v>10569</v>
+        <v>10608</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C48" s="4">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="D48" s="3">
         <v>13</v>
       </c>
-      <c r="E48" s="6" t="e">
-        <v>#N/A</v>
+      <c r="E48" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <v>10569</v>
+        <v>12262</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C49" s="4">
-        <v>150</v>
+        <v>468</v>
       </c>
       <c r="D49" s="3">
         <v>13</v>
       </c>
-      <c r="E49" s="6" t="e">
-        <v>#N/A</v>
+      <c r="E49" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
-        <v>10573</v>
+        <v>12492</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C50" s="4">
-        <v>232.1</v>
+        <v>2694.5</v>
       </c>
       <c r="D50" s="3">
         <v>13</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>41</v>
+      <c r="E50" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
-        <v>10608</v>
+        <v>12494</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C51" s="4">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D51" s="3">
         <v>13</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>5</v>
+      <c r="E51" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
-        <v>12262</v>
+        <v>12494</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C52" s="4">
-        <v>468</v>
+        <v>1311</v>
       </c>
       <c r="D52" s="3">
         <v>13</v>
       </c>
-      <c r="E52" s="6" t="s">
-        <v>81</v>
+      <c r="E52" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <v>12390</v>
+        <v>12494</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C53" s="4">
-        <v>50</v>
+        <v>1493</v>
       </c>
       <c r="D53" s="3">
         <v>13</v>
       </c>
-      <c r="E53" s="6" t="e">
-        <v>#N/A</v>
+      <c r="E53" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
-        <v>12390</v>
+        <v>13485</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C54" s="4">
-        <v>100</v>
+        <v>4341</v>
       </c>
       <c r="D54" s="3">
         <v>13</v>
       </c>
-      <c r="E54" s="6" t="e">
-        <v>#N/A</v>
+      <c r="E54" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
-        <v>12492</v>
+        <v>13486</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C55" s="4">
-        <v>2694.5</v>
+        <v>7180</v>
       </c>
       <c r="D55" s="3">
         <v>13</v>
       </c>
-      <c r="E55" s="6" t="s">
-        <v>83</v>
+      <c r="E55" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
-        <v>12494</v>
+        <v>14479</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C56" s="4">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D56" s="3">
         <v>13</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>83</v>
+      <c r="E56" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
-        <v>12494</v>
+        <v>14479</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C57" s="4">
-        <v>1311</v>
+        <v>1103.5</v>
       </c>
       <c r="D57" s="3">
         <v>13</v>
       </c>
-      <c r="E57" s="6" t="s">
-        <v>83</v>
+      <c r="E57" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
-        <v>12494</v>
+        <v>14479</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C58" s="4">
-        <v>1493</v>
+        <v>12320</v>
       </c>
       <c r="D58" s="3">
         <v>13</v>
       </c>
-      <c r="E58" s="6" t="s">
-        <v>83</v>
+      <c r="E58" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
-        <v>13485</v>
+        <v>14730</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C59" s="4">
-        <v>4741</v>
+        <v>2170</v>
       </c>
       <c r="D59" s="3">
         <v>13</v>
       </c>
-      <c r="E59" s="6" t="s">
-        <v>81</v>
+      <c r="E59" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <v>13486</v>
+        <v>16048</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C60" s="4">
-        <v>10280</v>
+        <v>3017</v>
       </c>
       <c r="D60" s="3">
         <v>13</v>
       </c>
-      <c r="E60" s="6" t="s">
-        <v>81</v>
+      <c r="E60" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <v>14479</v>
+        <v>16904</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="C61" s="4">
-        <v>50</v>
+        <v>9864</v>
       </c>
       <c r="D61" s="3">
         <v>13</v>
       </c>
-      <c r="E61" s="6" t="s">
-        <v>82</v>
+      <c r="E61" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <v>14479</v>
+        <v>16905</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C62" s="4">
-        <v>2703.5</v>
+        <v>3645</v>
       </c>
       <c r="D62" s="3">
         <v>13</v>
       </c>
-      <c r="E62" s="6" t="s">
-        <v>82</v>
+      <c r="E62" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
-        <v>14479</v>
+        <v>17065</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C63" s="4">
-        <v>12320</v>
+        <v>4730</v>
       </c>
       <c r="D63" s="3">
         <v>13</v>
       </c>
-      <c r="E63" s="6" t="s">
-        <v>82</v>
+      <c r="E63" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
-        <v>14730</v>
+        <v>17611</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C64" s="4">
-        <v>2170</v>
+        <v>190</v>
       </c>
       <c r="D64" s="3">
         <v>13</v>
       </c>
-      <c r="E64" s="6" t="s">
+      <c r="E64" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
-        <v>16048</v>
+        <v>17612</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C65" s="4">
-        <v>3017</v>
+        <v>40</v>
       </c>
       <c r="D65" s="3">
         <v>13</v>
       </c>
-      <c r="E65" s="6" t="s">
+      <c r="E65" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
-        <v>16904</v>
+        <v>30099</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C66" s="4">
-        <v>11264</v>
+        <v>2392</v>
       </c>
       <c r="D66" s="3">
         <v>13</v>
       </c>
-      <c r="E66" s="6" t="s">
-        <v>81</v>
+      <c r="E66" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
-        <v>16905</v>
+        <v>30100</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C67" s="4">
-        <v>4845</v>
+        <v>1520</v>
       </c>
       <c r="D67" s="3">
         <v>13</v>
       </c>
-      <c r="E67" s="6" t="s">
-        <v>81</v>
+      <c r="E67" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
-        <v>17065</v>
+        <v>30100</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C68" s="4">
-        <v>4730</v>
+        <v>3573</v>
       </c>
       <c r="D68" s="3">
         <v>13</v>
       </c>
-      <c r="E68" s="6" t="s">
-        <v>84</v>
+      <c r="E68" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
-        <v>17611</v>
+        <v>30101</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C69" s="4">
-        <v>440</v>
+        <v>372</v>
       </c>
       <c r="D69" s="3">
         <v>13</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>85</v>
+      <c r="E69" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
-        <v>17612</v>
+        <v>30101</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C70" s="4">
-        <v>40</v>
+        <v>3802</v>
       </c>
       <c r="D70" s="3">
         <v>13</v>
       </c>
-      <c r="E70" s="6" t="s">
-        <v>85</v>
+      <c r="E70" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
-        <v>30099</v>
+        <v>30102</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C71" s="4">
-        <v>1827</v>
+        <v>1740</v>
       </c>
       <c r="D71" s="3">
         <v>13</v>
       </c>
-      <c r="E71" s="6" t="s">
-        <v>81</v>
+      <c r="E71" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
-        <v>30099</v>
+        <v>30103</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C72" s="4">
-        <v>2110</v>
+        <v>1192</v>
       </c>
       <c r="D72" s="3">
         <v>13</v>
       </c>
-      <c r="E72" s="6" t="s">
-        <v>81</v>
+      <c r="E72" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
-        <v>30100</v>
+        <v>30103</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C73" s="4">
-        <v>1520</v>
+        <v>3395</v>
       </c>
       <c r="D73" s="3">
         <v>13</v>
       </c>
-      <c r="E73" s="6" t="s">
-        <v>81</v>
+      <c r="E73" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
-        <v>30100</v>
+        <v>30104</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C74" s="4">
-        <v>3573</v>
+        <v>2060</v>
       </c>
       <c r="D74" s="3">
         <v>13</v>
       </c>
-      <c r="E74" s="6" t="s">
-        <v>81</v>
+      <c r="E74" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <v>30101</v>
+        <v>30104</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C75" s="4">
-        <v>392</v>
+        <v>7767</v>
       </c>
       <c r="D75" s="3">
         <v>13</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>81</v>
+      <c r="E75" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <v>30101</v>
+        <v>30105</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C76" s="4">
-        <v>3802</v>
+        <v>1231</v>
       </c>
       <c r="D76" s="3">
         <v>13</v>
       </c>
-      <c r="E76" s="6" t="s">
-        <v>81</v>
+      <c r="E76" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <v>30102</v>
+        <v>30106</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C77" s="4">
-        <v>200</v>
+        <v>2970</v>
       </c>
       <c r="D77" s="3">
         <v>13</v>
       </c>
-      <c r="E77" s="6" t="s">
-        <v>81</v>
+      <c r="E77" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <v>30102</v>
+        <v>30106</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C78" s="4">
-        <v>7540</v>
+        <v>3875</v>
       </c>
       <c r="D78" s="3">
         <v>13</v>
       </c>
-      <c r="E78" s="6" t="s">
-        <v>81</v>
+      <c r="E78" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
-        <v>30103</v>
+        <v>30107</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C79" s="4">
-        <v>1212</v>
+        <v>1482</v>
       </c>
       <c r="D79" s="3">
         <v>13</v>
       </c>
-      <c r="E79" s="6" t="s">
-        <v>81</v>
+      <c r="E79" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <v>30103</v>
+        <v>30108</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C80" s="4">
-        <v>3395</v>
+        <v>150</v>
       </c>
       <c r="D80" s="3">
         <v>13</v>
       </c>
-      <c r="E80" s="6" t="s">
-        <v>81</v>
+      <c r="E80" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <v>30104</v>
+        <v>30108</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C81" s="4">
-        <v>2305</v>
+        <v>3904</v>
       </c>
       <c r="D81" s="3">
         <v>13</v>
       </c>
-      <c r="E81" s="6" t="s">
-        <v>81</v>
+      <c r="E81" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
-        <v>30104</v>
+        <v>30109</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C82" s="4">
-        <v>7767</v>
+        <v>150</v>
       </c>
       <c r="D82" s="3">
         <v>13</v>
       </c>
-      <c r="E82" s="6" t="s">
-        <v>81</v>
+      <c r="E82" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
-        <v>30105</v>
+        <v>30109</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C83" s="4">
-        <v>1231</v>
+        <v>5932</v>
       </c>
       <c r="D83" s="3">
         <v>13</v>
       </c>
-      <c r="E83" s="6" t="s">
-        <v>81</v>
+      <c r="E83" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
-        <v>30106</v>
+        <v>30110</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C84" s="4">
-        <v>2970</v>
+        <v>150</v>
       </c>
       <c r="D84" s="3">
         <v>13</v>
       </c>
-      <c r="E84" s="6" t="s">
-        <v>81</v>
+      <c r="E84" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
-        <v>30106</v>
+        <v>30110</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C85" s="4">
-        <v>3875</v>
+        <v>3540</v>
       </c>
       <c r="D85" s="3">
         <v>13</v>
       </c>
-      <c r="E85" s="6" t="s">
-        <v>81</v>
+      <c r="E85" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
-        <v>30107</v>
+        <v>30111</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C86" s="4">
-        <v>1482</v>
+        <v>150</v>
       </c>
       <c r="D86" s="3">
         <v>13</v>
       </c>
-      <c r="E86" s="6" t="s">
-        <v>81</v>
+      <c r="E86" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
-        <v>30108</v>
+        <v>30111</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C87" s="4">
-        <v>150</v>
+        <v>2370</v>
       </c>
       <c r="D87" s="3">
         <v>13</v>
       </c>
-      <c r="E87" s="6" t="s">
-        <v>81</v>
+      <c r="E87" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
-        <v>30108</v>
+        <v>30113</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C88" s="4">
-        <v>3904</v>
+        <v>830</v>
       </c>
       <c r="D88" s="3">
         <v>13</v>
       </c>
-      <c r="E88" s="6" t="s">
-        <v>81</v>
+      <c r="E88" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <v>30109</v>
+        <v>30113</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C89" s="4">
-        <v>150</v>
+        <v>3218</v>
       </c>
       <c r="D89" s="3">
         <v>13</v>
       </c>
-      <c r="E89" s="6" t="s">
-        <v>81</v>
+      <c r="E89" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <v>30109</v>
+        <v>30117</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C90" s="4">
-        <v>5932</v>
+        <v>2845</v>
       </c>
       <c r="D90" s="3">
         <v>13</v>
       </c>
-      <c r="E90" s="6" t="s">
-        <v>81</v>
+      <c r="E90" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
-        <v>30110</v>
+        <v>30117</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C91" s="4">
-        <v>150</v>
+        <v>4951</v>
       </c>
       <c r="D91" s="3">
         <v>13</v>
       </c>
-      <c r="E91" s="6" t="s">
-        <v>81</v>
+      <c r="E91" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
-        <v>30110</v>
+        <v>30118</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C92" s="4">
-        <v>3540</v>
+        <v>150</v>
       </c>
       <c r="D92" s="3">
         <v>13</v>
       </c>
-      <c r="E92" s="6" t="s">
-        <v>81</v>
+      <c r="E92" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
-        <v>30111</v>
+        <v>30118</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C93" s="4">
-        <v>150</v>
+        <v>2246</v>
       </c>
       <c r="D93" s="3">
         <v>13</v>
       </c>
-      <c r="E93" s="6" t="s">
-        <v>81</v>
+      <c r="E93" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="3">
-        <v>30111</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C94" s="4">
-        <v>2370</v>
-      </c>
-      <c r="D94" s="3">
-        <v>13</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>81</v>
-      </c>
+      <c r="A94" s="3"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="3"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="3">
-        <v>30113</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C95" s="4">
-        <v>830</v>
-      </c>
-      <c r="D95" s="3">
-        <v>13</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>81</v>
-      </c>
+      <c r="A95" s="3"/>
+      <c r="B95" s="1"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="3"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="3">
-        <v>30113</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C96" s="4">
-        <v>3218</v>
-      </c>
-      <c r="D96" s="3">
-        <v>13</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="3">
-        <v>30117</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C97" s="4">
-        <v>2870</v>
-      </c>
-      <c r="D97" s="3">
-        <v>13</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="3">
-        <v>30117</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C98" s="4">
-        <v>4951</v>
-      </c>
-      <c r="D98" s="3">
-        <v>13</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="3">
-        <v>30118</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C99" s="4">
-        <v>150</v>
-      </c>
-      <c r="D99" s="3">
-        <v>13</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="3">
-        <v>30118</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C100" s="4">
-        <v>2246</v>
-      </c>
-      <c r="D100" s="3">
-        <v>13</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>81</v>
-      </c>
+      <c r="A96" s="3"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="3"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="3"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="3"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="3"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="3"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="3"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="3"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="3"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E100" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/data-source/ESTOQUEBASESLOCAL.xlsx
+++ b/data-source/ESTOQUEBASESLOCAL.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\OneDrive\Área de Trabalho\SMART-STOCK\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{43BF1184-79C9-48E4-96C7-0517BAC7DE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13935F81-51DC-4872-B174-3FEF7CC5B373}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63034938-BC20-4E5E-913C-1B8AF110E434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha!$A$1:$E$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha!$A$1:$E$231</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Planilha!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -90,202 +90,202 @@
     <t>NAPA CEDRO ROSA 1.0 (PVC)</t>
   </si>
   <si>
+    <t>BASE COMFY</t>
+  </si>
+  <si>
+    <t>BASE GLITTER 1.0 SILVER</t>
+  </si>
+  <si>
+    <t>BASE GLITTER</t>
+  </si>
+  <si>
+    <t>NEW BASE FLEX 0.95MM - DARK GRAY</t>
+  </si>
+  <si>
+    <t>BASE ECO FLEX 0.95MM - DARK GRAY</t>
+  </si>
+  <si>
+    <t>BASE ECO FLEX 0.95MM - BISCOITO</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - BLACK</t>
+  </si>
+  <si>
+    <t>NEW BASE VITÓRIA WZ 1.1  BEGE 435</t>
+  </si>
+  <si>
+    <t>NEW BASE VITÓRIA WZ 1.1 WHITE</t>
+  </si>
+  <si>
+    <t>NEW BASE FLEX 1.0  BISCOITO</t>
+  </si>
+  <si>
+    <t>NEW BASE FLEX 1.0 DARK GRAY</t>
+  </si>
+  <si>
+    <t>NAPA CEDRO PRETO 7001 1.0MM (PVC)</t>
+  </si>
+  <si>
+    <t>NAPA CEDRO NUDE 658 1.0MM (PVC)</t>
+  </si>
+  <si>
+    <t>BASE PVC WHITE - COM PAPEL CASCO</t>
+  </si>
+  <si>
+    <t>NAPA BASE PVC</t>
+  </si>
+  <si>
+    <t>BASE GLITTER 1.0 BLACK</t>
+  </si>
+  <si>
+    <t>NAPA CEDRO BRANCO OFF (PVC)</t>
+  </si>
+  <si>
+    <t>NAPA CEDRO CINZA (PVC)</t>
+  </si>
+  <si>
+    <t>NAPA CEDRO CREME (PVC)</t>
+  </si>
+  <si>
+    <t>NAPA CEDRO ECO 1.0MM (PVC) PRETO</t>
+  </si>
+  <si>
+    <t>NEW BASE VITÓRIA WZ 1.1 SILVER</t>
+  </si>
+  <si>
+    <t>VELVET JOLIE STAR - PRETO</t>
+  </si>
+  <si>
+    <t>TECIDO VELVET</t>
+  </si>
+  <si>
+    <t>NEW BASE VITÓRIA WZ 1.1 CREME</t>
+  </si>
+  <si>
+    <t>VELVET JOLIE  PRETO LAMINADO QUADRICULADO Q072</t>
+  </si>
+  <si>
+    <t>SUEDE HOLLAND PREMIUM - 901 EUROTEXTIL - CINZA</t>
+  </si>
+  <si>
+    <t>NEW BASE FLEX 0.95 BISCOITO</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - BEGE</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - WHITE</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - CREME</t>
+  </si>
+  <si>
+    <t>BASE PEQUIM PU 1.0MM - BEGE</t>
+  </si>
+  <si>
+    <t>BASE PEQUIM PU 1.0MM - PRETO</t>
+  </si>
+  <si>
+    <t>NEW BASE VITÓRIA WZ 1.1 BLACK (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>NEW BASE VITÓRIA WZ 1.1 WHITE COM MARCA D'AGUA</t>
+  </si>
+  <si>
+    <t>NEW BASE VITÓRIA WZ 1.1 CASTANHO</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - CASTANHO</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - OFF WHITE</t>
+  </si>
+  <si>
+    <t>BASE SHENZHEN PU 1,05MM BEGE</t>
+  </si>
+  <si>
+    <t>BASE STRETCH 0,85 - NEGRO</t>
+  </si>
+  <si>
+    <t>BASE STRETCH 0,85 - BISCOITO</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - BEGE 626 (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - BLUSH (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - MENTA (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - NUDE (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - LAGOA AZUL (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - OFF WHITE 526 (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - ROSE (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - CAMEL 1165 (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - CANELA (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - CARAMELO (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - CASTOR (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - CONHAQUE (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - MEL (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - BORDO (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - CAFE</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - MILITAR (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>NAPA SARDENHA</t>
+  </si>
+  <si>
+    <t>NAPA CEDRO</t>
+  </si>
+  <si>
+    <t>NEW BASE VITÓRIA WZ</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI</t>
+  </si>
+  <si>
+    <t>BASE PEQUIM</t>
+  </si>
+  <si>
+    <t>BASE SHENZHEN</t>
+  </si>
+  <si>
+    <t>BASE STRETCH</t>
+  </si>
+  <si>
+    <t>BASE SUPREME CHASSI</t>
+  </si>
+  <si>
     <t>BASE COMFY SKIN 1.4 WHITE</t>
   </si>
   <si>
-    <t>BASE COMFY</t>
-  </si>
-  <si>
     <t>BASE COMFY SKIN 1.4 BEGE 435</t>
-  </si>
-  <si>
-    <t>BASE GLITTER 1.0 SILVER</t>
-  </si>
-  <si>
-    <t>BASE GLITTER</t>
-  </si>
-  <si>
-    <t>NEW BASE FLEX 0.95MM - DARK GRAY</t>
-  </si>
-  <si>
-    <t>BASE ECO FLEX 0.95MM - DARK GRAY</t>
-  </si>
-  <si>
-    <t>BASE ECO FLEX 0.95MM - BISCOITO</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - BLACK</t>
-  </si>
-  <si>
-    <t>NEW BASE VITÓRIA WZ 1.1  BEGE 435</t>
-  </si>
-  <si>
-    <t>NEW BASE VITÓRIA WZ 1.1 WHITE</t>
-  </si>
-  <si>
-    <t>NEW BASE FLEX 1.0  BISCOITO</t>
-  </si>
-  <si>
-    <t>NEW BASE FLEX 1.0 DARK GRAY</t>
-  </si>
-  <si>
-    <t>NAPA CEDRO PRETO 7001 1.0MM (PVC)</t>
-  </si>
-  <si>
-    <t>NAPA CEDRO NUDE 658 1.0MM (PVC)</t>
-  </si>
-  <si>
-    <t>BASE PVC WHITE - COM PAPEL CASCO</t>
-  </si>
-  <si>
-    <t>NAPA BASE PVC</t>
-  </si>
-  <si>
-    <t>BASE GLITTER 1.0 BLACK</t>
-  </si>
-  <si>
-    <t>NAPA CEDRO BRANCO OFF (PVC)</t>
-  </si>
-  <si>
-    <t>NAPA CEDRO CINZA (PVC)</t>
-  </si>
-  <si>
-    <t>NAPA CEDRO CREME (PVC)</t>
-  </si>
-  <si>
-    <t>NAPA CEDRO ECO 1.0MM (PVC) PRETO</t>
-  </si>
-  <si>
-    <t>NEW BASE VITÓRIA WZ 1.1 SILVER</t>
-  </si>
-  <si>
-    <t>VELVET JOLIE STAR - PRETO</t>
-  </si>
-  <si>
-    <t>TECIDO VELVET</t>
-  </si>
-  <si>
-    <t>NEW BASE VITÓRIA WZ 1.1 CREME</t>
-  </si>
-  <si>
-    <t>VELVET JOLIE  PRETO LAMINADO QUADRICULADO Q072</t>
-  </si>
-  <si>
-    <t>SUEDE HOLLAND PREMIUM - 901 EUROTEXTIL - CINZA</t>
-  </si>
-  <si>
-    <t>NEW BASE FLEX 0.95 BISCOITO</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - BEGE</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - WHITE</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - CREME</t>
-  </si>
-  <si>
-    <t>BASE PEQUIM PU 1.0MM - BEGE</t>
-  </si>
-  <si>
-    <t>BASE PEQUIM PU 1.0MM - PRETO</t>
-  </si>
-  <si>
-    <t>NEW BASE VITÓRIA WZ 1.1 BLACK (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
-    <t>NEW BASE VITÓRIA WZ 1.1 WHITE COM MARCA D'AGUA</t>
-  </si>
-  <si>
-    <t>NEW BASE VITÓRIA WZ 1.1 CASTANHO</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - CASTANHO</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - OFF WHITE</t>
-  </si>
-  <si>
-    <t>BASE SHENZHEN PU 1,05MM BEGE</t>
-  </si>
-  <si>
-    <t>BASE STRETCH 0,85 - NEGRO</t>
-  </si>
-  <si>
-    <t>BASE STRETCH 0,85 - BISCOITO</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - BEGE 626 (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - BLUSH (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - MENTA (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - NUDE (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - LAGOA AZUL (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - OFF WHITE 526 (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - ROSE (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - CAMEL 1165 (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - CANELA (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - CARAMELO (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - CASTOR (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - CONHAQUE (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - MEL (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - BORDO (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - CAFE</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 - MILITAR (COM MARCA D'AGUA)</t>
-  </si>
-  <si>
-    <t>BASE SUPREME CHASSI</t>
-  </si>
-  <si>
-    <t>NAPA SARDENHA</t>
-  </si>
-  <si>
-    <t>NAPA CEDRO</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI</t>
-  </si>
-  <si>
-    <t>NEW BASE VITÓRIA WZ</t>
-  </si>
-  <si>
-    <t>BASE PEQUIM</t>
-  </si>
-  <si>
-    <t>BASE SHENZHEN</t>
-  </si>
-  <si>
-    <t>BASE STRETCH</t>
   </si>
 </sst>
 </file>
@@ -694,14 +694,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E231"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="54.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -769,7 +769,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -786,7 +786,7 @@
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -803,7 +803,7 @@
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -854,7 +854,7 @@
         <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -871,7 +871,7 @@
         <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -888,7 +888,7 @@
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -905,7 +905,7 @@
         <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -922,7 +922,7 @@
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -939,7 +939,7 @@
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -956,7 +956,7 @@
         <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -964,7 +964,7 @@
         <v>8923</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="C16" s="4">
         <v>1160</v>
@@ -973,7 +973,7 @@
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -981,7 +981,7 @@
         <v>8924</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="C17" s="4">
         <v>1012</v>
@@ -990,7 +990,7 @@
         <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -998,7 +998,7 @@
         <v>8926</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C18" s="4">
         <v>4182</v>
@@ -1007,7 +1007,7 @@
         <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1015,7 +1015,7 @@
         <v>9004</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C19" s="4">
         <v>195</v>
@@ -1032,7 +1032,7 @@
         <v>9010</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20" s="4">
         <v>190</v>
@@ -1049,7 +1049,7 @@
         <v>9073</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" s="4">
         <v>194</v>
@@ -1066,16 +1066,16 @@
         <v>9091</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C22" s="4">
-        <v>32562.5</v>
+        <v>30942.5</v>
       </c>
       <c r="D22" s="3">
         <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1083,7 +1083,7 @@
         <v>9295</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C23" s="4">
         <v>902</v>
@@ -1092,7 +1092,7 @@
         <v>13</v>
       </c>
       <c r="E23" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1100,7 +1100,7 @@
         <v>9297</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C24" s="4">
         <v>100</v>
@@ -1109,7 +1109,7 @@
         <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1117,7 +1117,7 @@
         <v>9298</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C25" s="4">
         <v>137</v>
@@ -1134,7 +1134,7 @@
         <v>9300</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C26" s="4">
         <v>30</v>
@@ -1151,7 +1151,7 @@
         <v>9468</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C27" s="4">
         <v>50</v>
@@ -1168,7 +1168,7 @@
         <v>9468</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C28" s="4">
         <v>475</v>
@@ -1185,7 +1185,7 @@
         <v>9469</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C29" s="4">
         <v>49.7</v>
@@ -1202,7 +1202,7 @@
         <v>9469</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C30" s="4">
         <v>50</v>
@@ -1219,7 +1219,7 @@
         <v>9469</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C31" s="4">
         <v>473</v>
@@ -1236,7 +1236,7 @@
         <v>9573</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C32" s="4">
         <v>20.5</v>
@@ -1245,7 +1245,7 @@
         <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1253,7 +1253,7 @@
         <v>9573</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C33" s="4">
         <v>440</v>
@@ -1262,7 +1262,7 @@
         <v>13</v>
       </c>
       <c r="E33" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1270,7 +1270,7 @@
         <v>9614</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C34" s="4">
         <v>3250.5</v>
@@ -1279,7 +1279,7 @@
         <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1287,7 +1287,7 @@
         <v>9615</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C35" s="4">
         <v>50</v>
@@ -1296,7 +1296,7 @@
         <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1304,7 +1304,7 @@
         <v>9615</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C36" s="4">
         <v>60</v>
@@ -1313,7 +1313,7 @@
         <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1321,7 +1321,7 @@
         <v>9616</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C37" s="4">
         <v>309.3</v>
@@ -1330,7 +1330,7 @@
         <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1338,7 +1338,7 @@
         <v>9617</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C38" s="4">
         <v>50</v>
@@ -1347,7 +1347,7 @@
         <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1355,7 +1355,7 @@
         <v>9617</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C39" s="4">
         <v>113.7</v>
@@ -1364,7 +1364,7 @@
         <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1372,7 +1372,7 @@
         <v>9770</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C40" s="4">
         <v>57</v>
@@ -1381,7 +1381,7 @@
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1389,7 +1389,7 @@
         <v>9869</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C41" s="4">
         <v>707</v>
@@ -1398,7 +1398,7 @@
         <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1406,7 +1406,7 @@
         <v>10047</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C42" s="4">
         <v>0.6</v>
@@ -1415,7 +1415,7 @@
         <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1423,7 +1423,7 @@
         <v>10047</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C43" s="4">
         <v>1498</v>
@@ -1432,7 +1432,7 @@
         <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1440,7 +1440,7 @@
         <v>10103</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C44" s="4">
         <v>50</v>
@@ -1449,7 +1449,7 @@
         <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1457,7 +1457,7 @@
         <v>10103</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C45" s="4">
         <v>1026.5</v>
@@ -1466,7 +1466,7 @@
         <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1474,7 +1474,7 @@
         <v>10247</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C46" s="4">
         <v>1027</v>
@@ -1483,7 +1483,7 @@
         <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -1491,7 +1491,7 @@
         <v>10573</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C47" s="4">
         <v>232.1</v>
@@ -1500,7 +1500,7 @@
         <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -1508,7 +1508,7 @@
         <v>10608</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C48" s="4">
         <v>100</v>
@@ -1525,7 +1525,7 @@
         <v>12262</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C49" s="4">
         <v>468</v>
@@ -1534,7 +1534,7 @@
         <v>13</v>
       </c>
       <c r="E49" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -1542,7 +1542,7 @@
         <v>12492</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C50" s="4">
         <v>2694.5</v>
@@ -1551,7 +1551,7 @@
         <v>13</v>
       </c>
       <c r="E50" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -1559,7 +1559,7 @@
         <v>12494</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C51" s="4">
         <v>10</v>
@@ -1568,7 +1568,7 @@
         <v>13</v>
       </c>
       <c r="E51" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -1576,7 +1576,7 @@
         <v>12494</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C52" s="4">
         <v>1311</v>
@@ -1585,7 +1585,7 @@
         <v>13</v>
       </c>
       <c r="E52" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -1593,7 +1593,7 @@
         <v>12494</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C53" s="4">
         <v>1493</v>
@@ -1602,7 +1602,7 @@
         <v>13</v>
       </c>
       <c r="E53" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -1610,16 +1610,16 @@
         <v>13485</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C54" s="4">
-        <v>4341</v>
+        <v>1981</v>
       </c>
       <c r="D54" s="3">
         <v>13</v>
       </c>
       <c r="E54" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -1627,16 +1627,16 @@
         <v>13486</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C55" s="4">
-        <v>7180</v>
+        <v>5680</v>
       </c>
       <c r="D55" s="3">
         <v>13</v>
       </c>
       <c r="E55" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -1644,7 +1644,7 @@
         <v>14479</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C56" s="4">
         <v>50</v>
@@ -1653,7 +1653,7 @@
         <v>13</v>
       </c>
       <c r="E56" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -1661,7 +1661,7 @@
         <v>14479</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C57" s="4">
         <v>1103.5</v>
@@ -1670,7 +1670,7 @@
         <v>13</v>
       </c>
       <c r="E57" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -1678,7 +1678,7 @@
         <v>14479</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C58" s="4">
         <v>12320</v>
@@ -1687,7 +1687,7 @@
         <v>13</v>
       </c>
       <c r="E58" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -1695,7 +1695,7 @@
         <v>14730</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C59" s="4">
         <v>2170</v>
@@ -1704,7 +1704,7 @@
         <v>13</v>
       </c>
       <c r="E59" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -1712,7 +1712,7 @@
         <v>16048</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C60" s="4">
         <v>3017</v>
@@ -1721,7 +1721,7 @@
         <v>13</v>
       </c>
       <c r="E60" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -1729,16 +1729,16 @@
         <v>16904</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C61" s="4">
-        <v>9864</v>
+        <v>8349</v>
       </c>
       <c r="D61" s="3">
         <v>13</v>
       </c>
       <c r="E61" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -1746,16 +1746,16 @@
         <v>16905</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C62" s="4">
-        <v>3645</v>
+        <v>2645</v>
       </c>
       <c r="D62" s="3">
         <v>13</v>
       </c>
       <c r="E62" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -1763,7 +1763,7 @@
         <v>17065</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C63" s="4">
         <v>4730</v>
@@ -1772,7 +1772,7 @@
         <v>13</v>
       </c>
       <c r="E63" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -1780,7 +1780,7 @@
         <v>17611</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C64" s="4">
         <v>190</v>
@@ -1789,7 +1789,7 @@
         <v>13</v>
       </c>
       <c r="E64" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -1797,7 +1797,7 @@
         <v>17612</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C65" s="4">
         <v>40</v>
@@ -1806,7 +1806,7 @@
         <v>13</v>
       </c>
       <c r="E65" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -1814,16 +1814,16 @@
         <v>30099</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C66" s="4">
-        <v>2392</v>
+        <v>1392</v>
       </c>
       <c r="D66" s="3">
         <v>13</v>
       </c>
       <c r="E66" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -1831,7 +1831,7 @@
         <v>30100</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C67" s="4">
         <v>1520</v>
@@ -1840,7 +1840,7 @@
         <v>13</v>
       </c>
       <c r="E67" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -1848,7 +1848,7 @@
         <v>30100</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C68" s="4">
         <v>3573</v>
@@ -1857,7 +1857,7 @@
         <v>13</v>
       </c>
       <c r="E68" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -1865,7 +1865,7 @@
         <v>30101</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C69" s="4">
         <v>372</v>
@@ -1874,7 +1874,7 @@
         <v>13</v>
       </c>
       <c r="E69" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -1882,7 +1882,7 @@
         <v>30101</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C70" s="4">
         <v>3802</v>
@@ -1891,7 +1891,7 @@
         <v>13</v>
       </c>
       <c r="E70" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -1899,16 +1899,16 @@
         <v>30102</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C71" s="4">
-        <v>1740</v>
+        <v>1715</v>
       </c>
       <c r="D71" s="3">
         <v>13</v>
       </c>
       <c r="E71" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -1916,7 +1916,7 @@
         <v>30103</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C72" s="4">
         <v>1192</v>
@@ -1925,7 +1925,7 @@
         <v>13</v>
       </c>
       <c r="E72" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -1933,7 +1933,7 @@
         <v>30103</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C73" s="4">
         <v>3395</v>
@@ -1942,7 +1942,7 @@
         <v>13</v>
       </c>
       <c r="E73" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -1950,7 +1950,7 @@
         <v>30104</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C74" s="4">
         <v>2060</v>
@@ -1959,7 +1959,7 @@
         <v>13</v>
       </c>
       <c r="E74" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -1967,7 +1967,7 @@
         <v>30104</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C75" s="4">
         <v>7767</v>
@@ -1976,7 +1976,7 @@
         <v>13</v>
       </c>
       <c r="E75" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
@@ -1984,7 +1984,7 @@
         <v>30105</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C76" s="4">
         <v>1231</v>
@@ -1993,7 +1993,7 @@
         <v>13</v>
       </c>
       <c r="E76" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -2001,7 +2001,7 @@
         <v>30106</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C77" s="4">
         <v>2970</v>
@@ -2010,7 +2010,7 @@
         <v>13</v>
       </c>
       <c r="E77" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -2018,7 +2018,7 @@
         <v>30106</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C78" s="4">
         <v>3875</v>
@@ -2027,7 +2027,7 @@
         <v>13</v>
       </c>
       <c r="E78" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -2035,7 +2035,7 @@
         <v>30107</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C79" s="4">
         <v>1482</v>
@@ -2044,7 +2044,7 @@
         <v>13</v>
       </c>
       <c r="E79" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -2052,7 +2052,7 @@
         <v>30108</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C80" s="4">
         <v>150</v>
@@ -2061,7 +2061,7 @@
         <v>13</v>
       </c>
       <c r="E80" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -2069,7 +2069,7 @@
         <v>30108</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C81" s="4">
         <v>3904</v>
@@ -2078,7 +2078,7 @@
         <v>13</v>
       </c>
       <c r="E81" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -2086,7 +2086,7 @@
         <v>30109</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C82" s="4">
         <v>150</v>
@@ -2095,7 +2095,7 @@
         <v>13</v>
       </c>
       <c r="E82" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -2103,7 +2103,7 @@
         <v>30109</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C83" s="4">
         <v>5932</v>
@@ -2112,7 +2112,7 @@
         <v>13</v>
       </c>
       <c r="E83" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -2120,7 +2120,7 @@
         <v>30110</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C84" s="4">
         <v>150</v>
@@ -2129,7 +2129,7 @@
         <v>13</v>
       </c>
       <c r="E84" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -2137,7 +2137,7 @@
         <v>30110</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C85" s="4">
         <v>3540</v>
@@ -2146,7 +2146,7 @@
         <v>13</v>
       </c>
       <c r="E85" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -2154,7 +2154,7 @@
         <v>30111</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C86" s="4">
         <v>150</v>
@@ -2163,7 +2163,7 @@
         <v>13</v>
       </c>
       <c r="E86" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -2171,7 +2171,7 @@
         <v>30111</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C87" s="4">
         <v>2370</v>
@@ -2180,7 +2180,7 @@
         <v>13</v>
       </c>
       <c r="E87" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -2188,7 +2188,7 @@
         <v>30113</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C88" s="4">
         <v>830</v>
@@ -2197,7 +2197,7 @@
         <v>13</v>
       </c>
       <c r="E88" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -2205,7 +2205,7 @@
         <v>30113</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C89" s="4">
         <v>3218</v>
@@ -2214,7 +2214,7 @@
         <v>13</v>
       </c>
       <c r="E89" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -2222,7 +2222,7 @@
         <v>30117</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C90" s="4">
         <v>2845</v>
@@ -2231,7 +2231,7 @@
         <v>13</v>
       </c>
       <c r="E90" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -2239,7 +2239,7 @@
         <v>30117</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C91" s="4">
         <v>4951</v>
@@ -2248,7 +2248,7 @@
         <v>13</v>
       </c>
       <c r="E91" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -2256,7 +2256,7 @@
         <v>30118</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C92" s="4">
         <v>150</v>
@@ -2265,7 +2265,7 @@
         <v>13</v>
       </c>
       <c r="E92" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -2273,7 +2273,7 @@
         <v>30118</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C93" s="4">
         <v>2246</v>
@@ -2282,7 +2282,7 @@
         <v>13</v>
       </c>
       <c r="E93" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -2290,47 +2290,971 @@
       <c r="B94" s="1"/>
       <c r="C94" s="4"/>
       <c r="D94" s="3"/>
+      <c r="E94" s="1"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
       <c r="B95" s="1"/>
       <c r="C95" s="4"/>
       <c r="D95" s="3"/>
+      <c r="E95" s="1"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="1"/>
       <c r="C96" s="4"/>
       <c r="D96" s="3"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E96" s="1"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="1"/>
       <c r="C97" s="4"/>
       <c r="D97" s="3"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E97" s="1"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="1"/>
       <c r="C98" s="4"/>
       <c r="D98" s="3"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E98" s="1"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="1"/>
       <c r="C99" s="4"/>
       <c r="D99" s="3"/>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E99" s="1"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="1"/>
       <c r="C100" s="4"/>
       <c r="D100" s="3"/>
+      <c r="E100" s="1"/>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" s="3"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="1"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" s="3"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="1"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" s="3"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="1"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="3"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="1"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" s="3"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="4"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="1"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="3"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="1"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" s="3"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="1"/>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" s="3"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="4"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="1"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="3"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="1"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="3"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="4"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="1"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" s="3"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="4"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="1"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" s="3"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="4"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="1"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="3"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="4"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="1"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="3"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="4"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="1"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="3"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="4"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="1"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" s="3"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="4"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="1"/>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="3"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="4"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="1"/>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" s="3"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="4"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="1"/>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" s="3"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="4"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="1"/>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" s="3"/>
+      <c r="B120" s="1"/>
+      <c r="C120" s="4"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="1"/>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" s="3"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="4"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="1"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" s="3"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="4"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="1"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" s="3"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="4"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="1"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" s="3"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="4"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="1"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="3"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="4"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="1"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" s="3"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="4"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="1"/>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" s="3"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="4"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="1"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" s="3"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="4"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="1"/>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" s="3"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="4"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="1"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" s="3"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="4"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="1"/>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" s="3"/>
+      <c r="B131" s="1"/>
+      <c r="C131" s="4"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="1"/>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" s="3"/>
+      <c r="B132" s="1"/>
+      <c r="C132" s="4"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="1"/>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" s="3"/>
+      <c r="B133" s="1"/>
+      <c r="C133" s="4"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="1"/>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" s="3"/>
+      <c r="B134" s="1"/>
+      <c r="C134" s="4"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="1"/>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" s="3"/>
+      <c r="B135" s="1"/>
+      <c r="C135" s="4"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="1"/>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" s="3"/>
+      <c r="B136" s="1"/>
+      <c r="C136" s="4"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="1"/>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" s="3"/>
+      <c r="B137" s="1"/>
+      <c r="C137" s="4"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="1"/>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" s="3"/>
+      <c r="B138" s="1"/>
+      <c r="C138" s="4"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="1"/>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" s="3"/>
+      <c r="B139" s="1"/>
+      <c r="C139" s="4"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="1"/>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" s="3"/>
+      <c r="B140" s="1"/>
+      <c r="C140" s="4"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="1"/>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" s="3"/>
+      <c r="B141" s="1"/>
+      <c r="C141" s="4"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="1"/>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A142" s="3"/>
+      <c r="B142" s="1"/>
+      <c r="C142" s="4"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="1"/>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143" s="3"/>
+      <c r="B143" s="1"/>
+      <c r="C143" s="4"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="1"/>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144" s="3"/>
+      <c r="B144" s="1"/>
+      <c r="C144" s="4"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="1"/>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145" s="3"/>
+      <c r="B145" s="1"/>
+      <c r="C145" s="4"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="1"/>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146" s="3"/>
+      <c r="B146" s="1"/>
+      <c r="C146" s="4"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="1"/>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147" s="3"/>
+      <c r="B147" s="1"/>
+      <c r="C147" s="4"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="1"/>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148" s="3"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="4"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="1"/>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A149" s="3"/>
+      <c r="B149" s="1"/>
+      <c r="C149" s="4"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="1"/>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150" s="3"/>
+      <c r="B150" s="1"/>
+      <c r="C150" s="4"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="1"/>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A151" s="3"/>
+      <c r="B151" s="1"/>
+      <c r="C151" s="4"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="1"/>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A152" s="3"/>
+      <c r="B152" s="1"/>
+      <c r="C152" s="4"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="1"/>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A153" s="3"/>
+      <c r="B153" s="1"/>
+      <c r="C153" s="4"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="1"/>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A154" s="3"/>
+      <c r="B154" s="1"/>
+      <c r="C154" s="4"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="1"/>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A155" s="3"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="4"/>
+      <c r="D155" s="3"/>
+      <c r="E155" s="1"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A156" s="3"/>
+      <c r="B156" s="1"/>
+      <c r="C156" s="4"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="1"/>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A157" s="3"/>
+      <c r="B157" s="1"/>
+      <c r="C157" s="4"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="1"/>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A158" s="3"/>
+      <c r="B158" s="1"/>
+      <c r="C158" s="4"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="1"/>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A159" s="3"/>
+      <c r="B159" s="1"/>
+      <c r="C159" s="4"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="1"/>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A160" s="3"/>
+      <c r="B160" s="1"/>
+      <c r="C160" s="4"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="1"/>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A161" s="3"/>
+      <c r="B161" s="1"/>
+      <c r="C161" s="4"/>
+      <c r="D161" s="3"/>
+      <c r="E161" s="1"/>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A162" s="3"/>
+      <c r="B162" s="1"/>
+      <c r="C162" s="4"/>
+      <c r="D162" s="3"/>
+      <c r="E162" s="1"/>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A163" s="3"/>
+      <c r="B163" s="1"/>
+      <c r="C163" s="4"/>
+      <c r="D163" s="3"/>
+      <c r="E163" s="1"/>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A164" s="3"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="4"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="1"/>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A165" s="3"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="4"/>
+      <c r="D165" s="3"/>
+      <c r="E165" s="1"/>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A166" s="3"/>
+      <c r="B166" s="1"/>
+      <c r="C166" s="4"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="1"/>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A167" s="3"/>
+      <c r="B167" s="1"/>
+      <c r="C167" s="4"/>
+      <c r="D167" s="3"/>
+      <c r="E167" s="1"/>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A168" s="3"/>
+      <c r="B168" s="1"/>
+      <c r="C168" s="4"/>
+      <c r="D168" s="3"/>
+      <c r="E168" s="1"/>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A169" s="3"/>
+      <c r="B169" s="1"/>
+      <c r="C169" s="4"/>
+      <c r="D169" s="3"/>
+      <c r="E169" s="1"/>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A170" s="3"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="4"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="1"/>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A171" s="3"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="4"/>
+      <c r="D171" s="3"/>
+      <c r="E171" s="1"/>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172" s="3"/>
+      <c r="B172" s="1"/>
+      <c r="C172" s="4"/>
+      <c r="D172" s="3"/>
+      <c r="E172" s="1"/>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A173" s="3"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="4"/>
+      <c r="D173" s="3"/>
+      <c r="E173" s="1"/>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A174" s="3"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="4"/>
+      <c r="D174" s="3"/>
+      <c r="E174" s="1"/>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A175" s="3"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="4"/>
+      <c r="D175" s="3"/>
+      <c r="E175" s="1"/>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A176" s="3"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="4"/>
+      <c r="D176" s="3"/>
+      <c r="E176" s="1"/>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A177" s="3"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="4"/>
+      <c r="D177" s="3"/>
+      <c r="E177" s="1"/>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A178" s="3"/>
+      <c r="B178" s="1"/>
+      <c r="C178" s="4"/>
+      <c r="D178" s="3"/>
+      <c r="E178" s="1"/>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A179" s="3"/>
+      <c r="B179" s="1"/>
+      <c r="C179" s="4"/>
+      <c r="D179" s="3"/>
+      <c r="E179" s="1"/>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A180" s="3"/>
+      <c r="B180" s="1"/>
+      <c r="C180" s="4"/>
+      <c r="D180" s="3"/>
+      <c r="E180" s="1"/>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A181" s="3"/>
+      <c r="B181" s="1"/>
+      <c r="C181" s="4"/>
+      <c r="D181" s="3"/>
+      <c r="E181" s="1"/>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A182" s="3"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="4"/>
+      <c r="D182" s="3"/>
+      <c r="E182" s="1"/>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A183" s="3"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="4"/>
+      <c r="D183" s="3"/>
+      <c r="E183" s="1"/>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A184" s="3"/>
+      <c r="B184" s="1"/>
+      <c r="C184" s="4"/>
+      <c r="D184" s="3"/>
+      <c r="E184" s="1"/>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A185" s="3"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="4"/>
+      <c r="D185" s="3"/>
+      <c r="E185" s="1"/>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A186" s="3"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="4"/>
+      <c r="D186" s="3"/>
+      <c r="E186" s="1"/>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A187" s="3"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="4"/>
+      <c r="D187" s="3"/>
+      <c r="E187" s="1"/>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A188" s="3"/>
+      <c r="B188" s="1"/>
+      <c r="C188" s="4"/>
+      <c r="D188" s="3"/>
+      <c r="E188" s="1"/>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A189" s="3"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="4"/>
+      <c r="D189" s="3"/>
+      <c r="E189" s="1"/>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A190" s="3"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="4"/>
+      <c r="D190" s="3"/>
+      <c r="E190" s="1"/>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A191" s="3"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="4"/>
+      <c r="D191" s="3"/>
+      <c r="E191" s="1"/>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A192" s="3"/>
+      <c r="B192" s="1"/>
+      <c r="C192" s="4"/>
+      <c r="D192" s="3"/>
+      <c r="E192" s="1"/>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A193" s="3"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="4"/>
+      <c r="D193" s="3"/>
+      <c r="E193" s="1"/>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A194" s="3"/>
+      <c r="B194" s="1"/>
+      <c r="C194" s="4"/>
+      <c r="D194" s="3"/>
+      <c r="E194" s="1"/>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A195" s="3"/>
+      <c r="B195" s="1"/>
+      <c r="C195" s="4"/>
+      <c r="D195" s="3"/>
+      <c r="E195" s="1"/>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A196" s="3"/>
+      <c r="B196" s="1"/>
+      <c r="C196" s="4"/>
+      <c r="D196" s="3"/>
+      <c r="E196" s="1"/>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A197" s="3"/>
+      <c r="B197" s="1"/>
+      <c r="C197" s="4"/>
+      <c r="D197" s="3"/>
+      <c r="E197" s="1"/>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A198" s="3"/>
+      <c r="B198" s="1"/>
+      <c r="C198" s="4"/>
+      <c r="D198" s="3"/>
+      <c r="E198" s="1"/>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A199" s="3"/>
+      <c r="B199" s="1"/>
+      <c r="C199" s="4"/>
+      <c r="D199" s="3"/>
+      <c r="E199" s="1"/>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A200" s="3"/>
+      <c r="B200" s="1"/>
+      <c r="C200" s="4"/>
+      <c r="D200" s="3"/>
+      <c r="E200" s="1"/>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A201" s="3"/>
+      <c r="B201" s="1"/>
+      <c r="C201" s="4"/>
+      <c r="D201" s="3"/>
+      <c r="E201" s="1"/>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A202" s="3"/>
+      <c r="B202" s="1"/>
+      <c r="C202" s="4"/>
+      <c r="D202" s="3"/>
+      <c r="E202" s="1"/>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A203" s="3"/>
+      <c r="B203" s="1"/>
+      <c r="C203" s="4"/>
+      <c r="D203" s="3"/>
+      <c r="E203" s="1"/>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A204" s="3"/>
+      <c r="B204" s="1"/>
+      <c r="C204" s="4"/>
+      <c r="D204" s="3"/>
+      <c r="E204" s="1"/>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A205" s="3"/>
+      <c r="B205" s="1"/>
+      <c r="C205" s="4"/>
+      <c r="D205" s="3"/>
+      <c r="E205" s="1"/>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A206" s="3"/>
+      <c r="B206" s="1"/>
+      <c r="C206" s="4"/>
+      <c r="D206" s="3"/>
+      <c r="E206" s="1"/>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A207" s="3"/>
+      <c r="B207" s="1"/>
+      <c r="C207" s="4"/>
+      <c r="D207" s="3"/>
+      <c r="E207" s="1"/>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A208" s="3"/>
+      <c r="B208" s="1"/>
+      <c r="C208" s="4"/>
+      <c r="D208" s="3"/>
+      <c r="E208" s="1"/>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A209" s="3"/>
+      <c r="B209" s="1"/>
+      <c r="C209" s="4"/>
+      <c r="D209" s="3"/>
+      <c r="E209" s="1"/>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A210" s="3"/>
+      <c r="B210" s="1"/>
+      <c r="C210" s="4"/>
+      <c r="D210" s="3"/>
+      <c r="E210" s="1"/>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A211" s="3"/>
+      <c r="B211" s="1"/>
+      <c r="C211" s="4"/>
+      <c r="D211" s="3"/>
+      <c r="E211" s="1"/>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A212" s="3"/>
+      <c r="B212" s="1"/>
+      <c r="C212" s="4"/>
+      <c r="D212" s="3"/>
+      <c r="E212" s="1"/>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A213" s="3"/>
+      <c r="B213" s="1"/>
+      <c r="C213" s="4"/>
+      <c r="D213" s="3"/>
+      <c r="E213" s="1"/>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A214" s="3"/>
+      <c r="B214" s="1"/>
+      <c r="C214" s="4"/>
+      <c r="D214" s="3"/>
+      <c r="E214" s="1"/>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A215" s="3"/>
+      <c r="B215" s="1"/>
+      <c r="C215" s="4"/>
+      <c r="D215" s="3"/>
+      <c r="E215" s="1"/>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A216" s="3"/>
+      <c r="B216" s="1"/>
+      <c r="C216" s="4"/>
+      <c r="D216" s="3"/>
+      <c r="E216" s="1"/>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A217" s="3"/>
+      <c r="B217" s="1"/>
+      <c r="C217" s="4"/>
+      <c r="D217" s="3"/>
+      <c r="E217" s="1"/>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A218" s="3"/>
+      <c r="B218" s="1"/>
+      <c r="C218" s="4"/>
+      <c r="D218" s="3"/>
+      <c r="E218" s="1"/>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A219" s="3"/>
+      <c r="B219" s="1"/>
+      <c r="C219" s="4"/>
+      <c r="D219" s="3"/>
+      <c r="E219" s="1"/>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A220" s="3"/>
+      <c r="B220" s="1"/>
+      <c r="C220" s="4"/>
+      <c r="D220" s="3"/>
+      <c r="E220" s="1"/>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A221" s="3"/>
+      <c r="B221" s="1"/>
+      <c r="C221" s="4"/>
+      <c r="D221" s="3"/>
+      <c r="E221" s="1"/>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A222" s="3"/>
+      <c r="B222" s="1"/>
+      <c r="C222" s="4"/>
+      <c r="D222" s="3"/>
+      <c r="E222" s="1"/>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A223" s="3"/>
+      <c r="B223" s="1"/>
+      <c r="C223" s="4"/>
+      <c r="D223" s="3"/>
+      <c r="E223" s="1"/>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A224" s="3"/>
+      <c r="B224" s="1"/>
+      <c r="C224" s="4"/>
+      <c r="D224" s="3"/>
+      <c r="E224" s="1"/>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A225" s="3"/>
+      <c r="B225" s="1"/>
+      <c r="C225" s="4"/>
+      <c r="D225" s="3"/>
+      <c r="E225" s="1"/>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A226" s="3"/>
+      <c r="B226" s="1"/>
+      <c r="C226" s="4"/>
+      <c r="D226" s="3"/>
+      <c r="E226" s="1"/>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A227" s="3"/>
+      <c r="B227" s="1"/>
+      <c r="C227" s="4"/>
+      <c r="D227" s="3"/>
+      <c r="E227" s="1"/>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A228" s="3"/>
+      <c r="B228" s="1"/>
+      <c r="C228" s="4"/>
+      <c r="D228" s="3"/>
+      <c r="E228" s="1"/>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A229" s="3"/>
+      <c r="B229" s="1"/>
+      <c r="C229" s="4"/>
+      <c r="D229" s="3"/>
+      <c r="E229" s="1"/>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A230" s="3"/>
+      <c r="B230" s="1"/>
+      <c r="C230" s="4"/>
+      <c r="D230" s="3"/>
+      <c r="E230" s="1"/>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A231" s="3"/>
+      <c r="B231" s="1"/>
+      <c r="C231" s="4"/>
+      <c r="D231" s="3"/>
+      <c r="E231" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E100" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E231" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="9999" orientation="landscape"/>
+  <pageSetup paperSize="9" scale="14" fitToHeight="9999" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data-source/ESTOQUEBASESLOCAL.xlsx
+++ b/data-source/ESTOQUEBASESLOCAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\OneDrive\Área de Trabalho\SMART-STOCK\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63034938-BC20-4E5E-913C-1B8AF110E434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB19EB5-9CA3-40EE-AA44-4DE3D7A56BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="84">
   <si>
     <t>Produto</t>
   </si>
@@ -111,9 +111,6 @@
     <t>BASE SHANGHAI PU 1.05 - BLACK</t>
   </si>
   <si>
-    <t>NEW BASE VITÓRIA WZ 1.1  BEGE 435</t>
-  </si>
-  <si>
     <t>NEW BASE VITÓRIA WZ 1.1 WHITE</t>
   </si>
   <si>
@@ -286,6 +283,12 @@
   </si>
   <si>
     <t>BASE COMFY SKIN 1.4 BEGE 435</t>
+  </si>
+  <si>
+    <t>NEW BASE VITÓRIA WZ 1.1 BEGE 435 (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>BASE PEQUIM PU 1.0MM - BEGE 626</t>
   </si>
 </sst>
 </file>
@@ -769,7 +772,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -786,7 +789,7 @@
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -803,7 +806,7 @@
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -854,7 +857,7 @@
         <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -871,7 +874,7 @@
         <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -888,7 +891,7 @@
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -905,7 +908,7 @@
         <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -922,7 +925,7 @@
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -939,7 +942,7 @@
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -956,7 +959,7 @@
         <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -964,7 +967,7 @@
         <v>8923</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C16" s="4">
         <v>1160</v>
@@ -981,7 +984,7 @@
         <v>8924</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C17" s="4">
         <v>1012</v>
@@ -1069,24 +1072,24 @@
         <v>23</v>
       </c>
       <c r="C22" s="4">
-        <v>30942.5</v>
+        <v>11730</v>
       </c>
       <c r="D22" s="3">
         <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>9295</v>
+        <v>9091</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" s="4">
-        <v>902</v>
+        <v>28342.5</v>
       </c>
       <c r="D23" s="3">
         <v>13</v>
@@ -1100,7 +1103,7 @@
         <v>9297</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24" s="4">
         <v>100</v>
@@ -1109,7 +1112,7 @@
         <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1117,7 +1120,7 @@
         <v>9298</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" s="4">
         <v>137</v>
@@ -1134,7 +1137,7 @@
         <v>9300</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C26" s="4">
         <v>30</v>
@@ -1151,7 +1154,7 @@
         <v>9468</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="4">
         <v>50</v>
@@ -1168,10 +1171,10 @@
         <v>9468</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" s="4">
-        <v>475</v>
+        <v>275</v>
       </c>
       <c r="D28" s="3">
         <v>13</v>
@@ -1185,7 +1188,7 @@
         <v>9469</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" s="4">
         <v>49.7</v>
@@ -1202,7 +1205,7 @@
         <v>9469</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C30" s="4">
         <v>50</v>
@@ -1219,7 +1222,7 @@
         <v>9469</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C31" s="4">
         <v>473</v>
@@ -1236,7 +1239,7 @@
         <v>9573</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C32" s="4">
         <v>20.5</v>
@@ -1245,7 +1248,7 @@
         <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1253,7 +1256,7 @@
         <v>9573</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C33" s="4">
         <v>440</v>
@@ -1262,7 +1265,7 @@
         <v>13</v>
       </c>
       <c r="E33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1270,7 +1273,7 @@
         <v>9614</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C34" s="4">
         <v>3250.5</v>
@@ -1287,7 +1290,7 @@
         <v>9615</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C35" s="4">
         <v>50</v>
@@ -1296,7 +1299,7 @@
         <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1304,7 +1307,7 @@
         <v>9615</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36" s="4">
         <v>60</v>
@@ -1313,7 +1316,7 @@
         <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1321,7 +1324,7 @@
         <v>9616</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C37" s="4">
         <v>309.3</v>
@@ -1330,7 +1333,7 @@
         <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1338,7 +1341,7 @@
         <v>9617</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C38" s="4">
         <v>50</v>
@@ -1347,7 +1350,7 @@
         <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1355,7 +1358,7 @@
         <v>9617</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C39" s="4">
         <v>113.7</v>
@@ -1364,7 +1367,7 @@
         <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1372,7 +1375,7 @@
         <v>9770</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C40" s="4">
         <v>57</v>
@@ -1381,7 +1384,7 @@
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1389,16 +1392,16 @@
         <v>9869</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C41" s="4">
-        <v>707</v>
+        <v>487</v>
       </c>
       <c r="D41" s="3">
         <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1406,7 +1409,7 @@
         <v>10047</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C42" s="4">
         <v>0.6</v>
@@ -1415,7 +1418,7 @@
         <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1423,7 +1426,7 @@
         <v>10047</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C43" s="4">
         <v>1498</v>
@@ -1432,7 +1435,7 @@
         <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1440,7 +1443,7 @@
         <v>10103</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C44" s="4">
         <v>50</v>
@@ -1449,7 +1452,7 @@
         <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1457,7 +1460,7 @@
         <v>10103</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C45" s="4">
         <v>1026.5</v>
@@ -1466,7 +1469,7 @@
         <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1474,7 +1477,7 @@
         <v>10247</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C46" s="4">
         <v>1027</v>
@@ -1483,7 +1486,7 @@
         <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -1491,7 +1494,7 @@
         <v>10573</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C47" s="4">
         <v>232.1</v>
@@ -1500,7 +1503,7 @@
         <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -1508,7 +1511,7 @@
         <v>10608</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C48" s="4">
         <v>100</v>
@@ -1525,16 +1528,16 @@
         <v>12262</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C49" s="4">
-        <v>468</v>
+        <v>118</v>
       </c>
       <c r="D49" s="3">
         <v>13</v>
       </c>
       <c r="E49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -1542,7 +1545,7 @@
         <v>12492</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C50" s="4">
         <v>2694.5</v>
@@ -1551,7 +1554,7 @@
         <v>13</v>
       </c>
       <c r="E50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -1559,7 +1562,7 @@
         <v>12494</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C51" s="4">
         <v>10</v>
@@ -1568,7 +1571,7 @@
         <v>13</v>
       </c>
       <c r="E51" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -1576,16 +1579,16 @@
         <v>12494</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C52" s="4">
-        <v>1311</v>
+        <v>911</v>
       </c>
       <c r="D52" s="3">
         <v>13</v>
       </c>
       <c r="E52" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -1593,7 +1596,7 @@
         <v>12494</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C53" s="4">
         <v>1493</v>
@@ -1602,7 +1605,7 @@
         <v>13</v>
       </c>
       <c r="E53" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -1610,16 +1613,16 @@
         <v>13485</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C54" s="4">
-        <v>1981</v>
+        <v>946</v>
       </c>
       <c r="D54" s="3">
         <v>13</v>
       </c>
       <c r="E54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -1627,27 +1630,27 @@
         <v>13486</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C55" s="4">
-        <v>5680</v>
+        <v>30</v>
       </c>
       <c r="D55" s="3">
         <v>13</v>
       </c>
       <c r="E55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
-        <v>14479</v>
+        <v>13486</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C56" s="4">
-        <v>50</v>
+        <v>5620</v>
       </c>
       <c r="D56" s="3">
         <v>13</v>
@@ -1661,16 +1664,16 @@
         <v>14479</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C57" s="4">
-        <v>1103.5</v>
+        <v>50</v>
       </c>
       <c r="D57" s="3">
         <v>13</v>
       </c>
       <c r="E57" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -1678,745 +1681,935 @@
         <v>14479</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C58" s="4">
-        <v>12320</v>
+        <v>1103.5</v>
       </c>
       <c r="D58" s="3">
         <v>13</v>
       </c>
       <c r="E58" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
-        <v>14730</v>
+        <v>14479</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C59" s="4">
-        <v>2170</v>
+        <v>12320</v>
       </c>
       <c r="D59" s="3">
         <v>13</v>
       </c>
       <c r="E59" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <v>16048</v>
+        <v>14730</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C60" s="4">
-        <v>3017</v>
+        <v>670</v>
       </c>
       <c r="D60" s="3">
         <v>13</v>
       </c>
       <c r="E60" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <v>16904</v>
+        <v>16048</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C61" s="4">
-        <v>8349</v>
+        <v>3017</v>
       </c>
       <c r="D61" s="3">
         <v>13</v>
       </c>
       <c r="E61" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <v>16905</v>
+        <v>16904</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C62" s="4">
-        <v>2645</v>
+        <v>5734</v>
       </c>
       <c r="D62" s="3">
         <v>13</v>
       </c>
       <c r="E62" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
-        <v>17065</v>
+        <v>16905</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C63" s="4">
-        <v>4730</v>
+        <v>1415</v>
       </c>
       <c r="D63" s="3">
         <v>13</v>
       </c>
       <c r="E63" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
-        <v>17611</v>
+        <v>17065</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C64" s="4">
-        <v>190</v>
+        <v>4730</v>
       </c>
       <c r="D64" s="3">
         <v>13</v>
       </c>
       <c r="E64" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
-        <v>17612</v>
+        <v>17611</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C65" s="4">
-        <v>40</v>
+        <v>190</v>
       </c>
       <c r="D65" s="3">
         <v>13</v>
       </c>
       <c r="E65" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
-        <v>30099</v>
+        <v>17612</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C66" s="4">
-        <v>1392</v>
+        <v>40</v>
       </c>
       <c r="D66" s="3">
         <v>13</v>
       </c>
       <c r="E66" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
-        <v>30100</v>
+        <v>17929</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C67" s="4">
-        <v>1520</v>
+        <v>10053</v>
       </c>
       <c r="D67" s="3">
         <v>13</v>
       </c>
       <c r="E67" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
-        <v>30100</v>
+        <v>30099</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C68" s="4">
-        <v>3573</v>
+        <v>4737</v>
       </c>
       <c r="D68" s="3">
         <v>13</v>
       </c>
       <c r="E68" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
-        <v>30101</v>
+        <v>30100</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C69" s="4">
-        <v>372</v>
+        <v>30</v>
       </c>
       <c r="D69" s="3">
         <v>13</v>
       </c>
       <c r="E69" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
-        <v>30101</v>
+        <v>30100</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C70" s="4">
-        <v>3802</v>
+        <v>1520</v>
       </c>
       <c r="D70" s="3">
         <v>13</v>
       </c>
       <c r="E70" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
-        <v>30102</v>
+        <v>30100</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C71" s="4">
-        <v>1715</v>
+        <v>3513</v>
       </c>
       <c r="D71" s="3">
         <v>13</v>
       </c>
       <c r="E71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
-        <v>30103</v>
+        <v>30101</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C72" s="4">
-        <v>1192</v>
+        <v>30</v>
       </c>
       <c r="D72" s="3">
         <v>13</v>
       </c>
       <c r="E72" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
-        <v>30103</v>
+        <v>30101</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C73" s="4">
-        <v>3395</v>
+        <v>342</v>
       </c>
       <c r="D73" s="3">
         <v>13</v>
       </c>
       <c r="E73" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
-        <v>30104</v>
+        <v>30101</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C74" s="4">
-        <v>2060</v>
+        <v>3802</v>
       </c>
       <c r="D74" s="3">
         <v>13</v>
       </c>
       <c r="E74" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <v>30104</v>
+        <v>30102</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C75" s="4">
-        <v>7767</v>
+        <v>30</v>
       </c>
       <c r="D75" s="3">
         <v>13</v>
       </c>
       <c r="E75" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <v>30105</v>
+        <v>30102</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C76" s="4">
-        <v>1231</v>
+        <v>715</v>
       </c>
       <c r="D76" s="3">
         <v>13</v>
       </c>
       <c r="E76" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <v>30106</v>
+        <v>30103</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C77" s="4">
-        <v>2970</v>
+        <v>30</v>
       </c>
       <c r="D77" s="3">
         <v>13</v>
       </c>
       <c r="E77" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <v>30106</v>
+        <v>30103</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C78" s="4">
-        <v>3875</v>
+        <v>162</v>
       </c>
       <c r="D78" s="3">
         <v>13</v>
       </c>
       <c r="E78" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
-        <v>30107</v>
+        <v>30103</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C79" s="4">
-        <v>1482</v>
+        <v>3395</v>
       </c>
       <c r="D79" s="3">
         <v>13</v>
       </c>
       <c r="E79" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <v>30108</v>
+        <v>30104</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C80" s="4">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="D80" s="3">
         <v>13</v>
       </c>
       <c r="E80" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <v>30108</v>
+        <v>30104</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C81" s="4">
-        <v>3904</v>
+        <v>1830</v>
       </c>
       <c r="D81" s="3">
         <v>13</v>
       </c>
       <c r="E81" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
-        <v>30109</v>
+        <v>30104</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C82" s="4">
-        <v>150</v>
+        <v>7767</v>
       </c>
       <c r="D82" s="3">
         <v>13</v>
       </c>
       <c r="E82" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
-        <v>30109</v>
+        <v>30105</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C83" s="4">
-        <v>5932</v>
+        <v>30</v>
       </c>
       <c r="D83" s="3">
         <v>13</v>
       </c>
       <c r="E83" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
-        <v>30110</v>
+        <v>30105</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C84" s="4">
-        <v>150</v>
+        <v>1171</v>
       </c>
       <c r="D84" s="3">
         <v>13</v>
       </c>
       <c r="E84" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
-        <v>30110</v>
+        <v>30106</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C85" s="4">
-        <v>3540</v>
+        <v>30</v>
       </c>
       <c r="D85" s="3">
         <v>13</v>
       </c>
       <c r="E85" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
-        <v>30111</v>
+        <v>30106</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C86" s="4">
-        <v>150</v>
+        <v>1500</v>
       </c>
       <c r="D86" s="3">
         <v>13</v>
       </c>
       <c r="E86" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
-        <v>30111</v>
+        <v>30106</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C87" s="4">
-        <v>2370</v>
+        <v>3875</v>
       </c>
       <c r="D87" s="3">
         <v>13</v>
       </c>
       <c r="E87" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
-        <v>30113</v>
+        <v>30107</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C88" s="4">
-        <v>830</v>
+        <v>30</v>
       </c>
       <c r="D88" s="3">
         <v>13</v>
       </c>
       <c r="E88" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <v>30113</v>
+        <v>30107</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C89" s="4">
-        <v>3218</v>
+        <v>1252</v>
       </c>
       <c r="D89" s="3">
         <v>13</v>
       </c>
       <c r="E89" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <v>30117</v>
+        <v>30108</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C90" s="4">
-        <v>2845</v>
+        <v>30</v>
       </c>
       <c r="D90" s="3">
         <v>13</v>
       </c>
       <c r="E90" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
-        <v>30117</v>
+        <v>30108</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C91" s="4">
-        <v>4951</v>
+        <v>120</v>
       </c>
       <c r="D91" s="3">
         <v>13</v>
       </c>
       <c r="E91" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
-        <v>30118</v>
+        <v>30108</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C92" s="4">
-        <v>150</v>
+        <v>3904</v>
       </c>
       <c r="D92" s="3">
         <v>13</v>
       </c>
       <c r="E92" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
+        <v>30109</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C93" s="4">
+        <v>30</v>
+      </c>
+      <c r="D93" s="3">
+        <v>13</v>
+      </c>
+      <c r="E93" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="3">
+        <v>30109</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C94" s="4">
+        <v>90</v>
+      </c>
+      <c r="D94" s="3">
+        <v>13</v>
+      </c>
+      <c r="E94" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="3">
+        <v>30109</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C95" s="4">
+        <v>5932</v>
+      </c>
+      <c r="D95" s="3">
+        <v>13</v>
+      </c>
+      <c r="E95" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="3">
+        <v>30110</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C96" s="4">
+        <v>30</v>
+      </c>
+      <c r="D96" s="3">
+        <v>13</v>
+      </c>
+      <c r="E96" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="3">
+        <v>30110</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C97" s="4">
+        <v>2787</v>
+      </c>
+      <c r="D97" s="3">
+        <v>13</v>
+      </c>
+      <c r="E97" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="3">
+        <v>30110</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C98" s="4">
+        <v>3540</v>
+      </c>
+      <c r="D98" s="3">
+        <v>13</v>
+      </c>
+      <c r="E98" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="3">
+        <v>30111</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C99" s="4">
+        <v>30</v>
+      </c>
+      <c r="D99" s="3">
+        <v>13</v>
+      </c>
+      <c r="E99" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="3">
+        <v>30111</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C100" s="4">
+        <v>2370</v>
+      </c>
+      <c r="D100" s="3">
+        <v>13</v>
+      </c>
+      <c r="E100" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" s="3">
+        <v>30111</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C101" s="4">
+        <v>7781</v>
+      </c>
+      <c r="D101" s="3">
+        <v>13</v>
+      </c>
+      <c r="E101" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" s="3">
+        <v>30113</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C102" s="4">
+        <v>30</v>
+      </c>
+      <c r="D102" s="3">
+        <v>13</v>
+      </c>
+      <c r="E102" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" s="3">
+        <v>30113</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C103" s="4">
+        <v>830</v>
+      </c>
+      <c r="D103" s="3">
+        <v>13</v>
+      </c>
+      <c r="E103" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="3">
+        <v>30113</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C104" s="4">
+        <v>3431</v>
+      </c>
+      <c r="D104" s="3">
+        <v>13</v>
+      </c>
+      <c r="E104" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" s="3">
+        <v>30117</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C105" s="4">
+        <v>30</v>
+      </c>
+      <c r="D105" s="3">
+        <v>13</v>
+      </c>
+      <c r="E105" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="3">
+        <v>30117</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C106" s="4">
+        <v>2815</v>
+      </c>
+      <c r="D106" s="3">
+        <v>13</v>
+      </c>
+      <c r="E106" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" s="3">
+        <v>30117</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C107" s="4">
+        <v>4951</v>
+      </c>
+      <c r="D107" s="3">
+        <v>13</v>
+      </c>
+      <c r="E107" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" s="3">
         <v>30118</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C93" s="4">
+      <c r="B108" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C108" s="4">
+        <v>30</v>
+      </c>
+      <c r="D108" s="3">
+        <v>13</v>
+      </c>
+      <c r="E108" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="3">
+        <v>30118</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C109" s="4">
         <v>2246</v>
       </c>
-      <c r="D93" s="3">
-        <v>13</v>
-      </c>
-      <c r="E93" t="s">
+      <c r="D109" s="3">
+        <v>13</v>
+      </c>
+      <c r="E109" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="3">
+        <v>30118</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C110" s="4">
+        <v>2840</v>
+      </c>
+      <c r="D110" s="3">
+        <v>13</v>
+      </c>
+      <c r="E110" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" s="3">
+        <v>30169</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C111" s="4">
+        <v>50</v>
+      </c>
+      <c r="D111" s="3">
+        <v>13</v>
+      </c>
+      <c r="E111" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="3"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="1"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="3"/>
-      <c r="B95" s="1"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="1"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="3"/>
-      <c r="B96" s="1"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="3"/>
-      <c r="E96" s="1"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="3"/>
-      <c r="B97" s="1"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="1"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="3"/>
-      <c r="B98" s="1"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="1"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="3"/>
-      <c r="B99" s="1"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="1"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="3"/>
-      <c r="B100" s="1"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="1"/>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" s="3"/>
-      <c r="B101" s="1"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="3"/>
-      <c r="E101" s="1"/>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" s="3"/>
-      <c r="B102" s="1"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="3"/>
-      <c r="E102" s="1"/>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="3"/>
-      <c r="B103" s="1"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="1"/>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="3"/>
-      <c r="B104" s="1"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="3"/>
-      <c r="E104" s="1"/>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" s="3"/>
-      <c r="B105" s="1"/>
-      <c r="C105" s="4"/>
-      <c r="D105" s="3"/>
-      <c r="E105" s="1"/>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" s="3"/>
-      <c r="B106" s="1"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="3"/>
-      <c r="E106" s="1"/>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="3"/>
-      <c r="B107" s="1"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="3"/>
-      <c r="E107" s="1"/>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="3"/>
-      <c r="B108" s="1"/>
-      <c r="C108" s="4"/>
-      <c r="D108" s="3"/>
-      <c r="E108" s="1"/>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="3"/>
-      <c r="B109" s="1"/>
-      <c r="C109" s="4"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="1"/>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" s="3"/>
-      <c r="B110" s="1"/>
-      <c r="C110" s="4"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="1"/>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" s="3"/>
-      <c r="B111" s="1"/>
-      <c r="C111" s="4"/>
-      <c r="D111" s="3"/>
-      <c r="E111" s="1"/>
-    </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="3"/>
-      <c r="B112" s="1"/>
-      <c r="C112" s="4"/>
-      <c r="D112" s="3"/>
-      <c r="E112" s="1"/>
+      <c r="A112" s="3">
+        <v>30215</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C112" s="4">
+        <v>50</v>
+      </c>
+      <c r="D112" s="3">
+        <v>13</v>
+      </c>
+      <c r="E112" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="3"/>

--- a/data-source/ESTOQUEBASESLOCAL.xlsx
+++ b/data-source/ESTOQUEBASESLOCAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\OneDrive\Área de Trabalho\SMART-STOCK\data-source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB19EB5-9CA3-40EE-AA44-4DE3D7A56BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{623C5EE9-E726-4051-8B3C-7C3F13BD1A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA7D2625-C1D3-4A59-B542-289C19B43653}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="85">
   <si>
     <t>Produto</t>
   </si>
@@ -168,9 +168,6 @@
     <t>NEW BASE FLEX 0.95 BISCOITO</t>
   </si>
   <si>
-    <t>BASE SHANGHAI PU 1.05 - BEGE</t>
-  </si>
-  <si>
     <t>BASE SHANGHAI PU 1.05 - WHITE</t>
   </si>
   <si>
@@ -186,9 +183,6 @@
     <t>NEW BASE VITÓRIA WZ 1.1 BLACK (COM MARCA D'AGUA)</t>
   </si>
   <si>
-    <t>NEW BASE VITÓRIA WZ 1.1 WHITE COM MARCA D'AGUA</t>
-  </si>
-  <si>
     <t>NEW BASE VITÓRIA WZ 1.1 CASTANHO</t>
   </si>
   <si>
@@ -286,6 +280,15 @@
   </si>
   <si>
     <t>NEW BASE VITÓRIA WZ 1.1 BEGE 435 (COM MARCA D'AGUA)</t>
+  </si>
+  <si>
+    <t>NAPA TURIM PARA METALIZAR</t>
+  </si>
+  <si>
+    <t>TURIM</t>
+  </si>
+  <si>
+    <t>NAPA TURIM 1.0 BRANCO 99- BEIRA RIO</t>
   </si>
   <si>
     <t>BASE PEQUIM PU 1.0MM - BEGE 626</t>
@@ -766,64 +769,64 @@
         <v>8</v>
       </c>
       <c r="C4" s="4">
-        <v>311</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3">
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>6520</v>
+        <v>6518</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="4">
-        <v>2000</v>
+        <v>2842</v>
       </c>
       <c r="D5" s="3">
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>6594</v>
+        <v>6520</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="4">
-        <v>192</v>
+        <v>1700</v>
       </c>
       <c r="D6" s="3">
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>8007</v>
+        <v>6594</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="4">
-        <v>100</v>
+        <v>192</v>
       </c>
       <c r="D7" s="3">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -834,7 +837,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="4">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="D8" s="3">
         <v>13</v>
@@ -845,36 +848,36 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>8875</v>
+        <v>8007</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="4">
-        <v>359.6</v>
+        <v>188</v>
       </c>
       <c r="D9" s="3">
         <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>8879</v>
+        <v>8875</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10" s="4">
-        <v>76.5</v>
+        <v>359.6</v>
       </c>
       <c r="D10" s="3">
         <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -885,30 +888,30 @@
         <v>14</v>
       </c>
       <c r="C11" s="4">
-        <v>364</v>
+        <v>76.5</v>
       </c>
       <c r="D11" s="3">
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <v>8881</v>
+        <v>8879</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="4">
-        <v>18.7</v>
+        <v>364</v>
       </c>
       <c r="D12" s="3">
         <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -919,30 +922,30 @@
         <v>15</v>
       </c>
       <c r="C13" s="4">
-        <v>1077</v>
+        <v>18.7</v>
       </c>
       <c r="D13" s="3">
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>8882</v>
+        <v>8881</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" s="4">
-        <v>3.2</v>
+        <v>1077</v>
       </c>
       <c r="D14" s="3">
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -953,41 +956,41 @@
         <v>16</v>
       </c>
       <c r="C15" s="4">
-        <v>1240</v>
+        <v>3.2</v>
       </c>
       <c r="D15" s="3">
         <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>8923</v>
+        <v>8882</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="C16" s="4">
-        <v>1160</v>
+        <v>1240</v>
       </c>
       <c r="D16" s="3">
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>8924</v>
+        <v>8923</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C17" s="4">
-        <v>1012</v>
+        <v>1160</v>
       </c>
       <c r="D17" s="3">
         <v>13</v>
@@ -998,47 +1001,47 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>8926</v>
+        <v>8924</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="C18" s="4">
-        <v>4182</v>
+        <v>1012</v>
       </c>
       <c r="D18" s="3">
         <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>9004</v>
+        <v>8926</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C19" s="4">
-        <v>195</v>
+        <v>3662</v>
       </c>
       <c r="D19" s="3">
         <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>9010</v>
+        <v>9004</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20" s="4">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D20" s="3">
         <v>13</v>
@@ -1049,13 +1052,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>9073</v>
+        <v>9010</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" s="4">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D21" s="3">
         <v>13</v>
@@ -1066,19 +1069,19 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>9091</v>
+        <v>9073</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" s="4">
-        <v>11730</v>
+        <v>194</v>
       </c>
       <c r="D22" s="3">
         <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1089,58 +1092,58 @@
         <v>23</v>
       </c>
       <c r="C23" s="4">
-        <v>28342.5</v>
+        <v>11730</v>
       </c>
       <c r="D23" s="3">
         <v>13</v>
       </c>
       <c r="E23" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>9297</v>
+        <v>9091</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="4">
-        <v>100</v>
+        <v>26223.5</v>
       </c>
       <c r="D24" s="3">
         <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>9298</v>
+        <v>9297</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="4">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="D25" s="3">
         <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <v>9300</v>
+        <v>9298</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" s="4">
-        <v>30</v>
+        <v>137</v>
       </c>
       <c r="D26" s="3">
         <v>13</v>
@@ -1151,19 +1154,19 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>9468</v>
+        <v>9300</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" s="4">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D27" s="3">
         <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1174,7 +1177,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="4">
-        <v>275</v>
+        <v>50</v>
       </c>
       <c r="D28" s="3">
         <v>13</v>
@@ -1185,13 +1188,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <v>9469</v>
+        <v>9468</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" s="4">
-        <v>49.7</v>
+        <v>275</v>
       </c>
       <c r="D29" s="3">
         <v>13</v>
@@ -1208,7 +1211,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="4">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="D30" s="3">
         <v>13</v>
@@ -1225,7 +1228,7 @@
         <v>28</v>
       </c>
       <c r="C31" s="4">
-        <v>473</v>
+        <v>50</v>
       </c>
       <c r="D31" s="3">
         <v>13</v>
@@ -1236,19 +1239,19 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
-        <v>9573</v>
+        <v>9469</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C32" s="4">
-        <v>20.5</v>
+        <v>473</v>
       </c>
       <c r="D32" s="3">
         <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1259,7 +1262,7 @@
         <v>29</v>
       </c>
       <c r="C33" s="4">
-        <v>440</v>
+        <v>20.5</v>
       </c>
       <c r="D33" s="3">
         <v>13</v>
@@ -1270,36 +1273,36 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
-        <v>9614</v>
+        <v>9573</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C34" s="4">
-        <v>3250.5</v>
+        <v>440</v>
       </c>
       <c r="D34" s="3">
         <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <v>9615</v>
+        <v>9614</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" s="4">
-        <v>50</v>
+        <v>3050.5</v>
       </c>
       <c r="D35" s="3">
         <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1310,47 +1313,47 @@
         <v>32</v>
       </c>
       <c r="C36" s="4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D36" s="3">
         <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
-        <v>9616</v>
+        <v>9615</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C37" s="4">
-        <v>309.3</v>
+        <v>60</v>
       </c>
       <c r="D37" s="3">
         <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
-        <v>9617</v>
+        <v>9616</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C38" s="4">
-        <v>50</v>
+        <v>309.3</v>
       </c>
       <c r="D38" s="3">
         <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1361,64 +1364,64 @@
         <v>34</v>
       </c>
       <c r="C39" s="4">
-        <v>113.7</v>
+        <v>50</v>
       </c>
       <c r="D39" s="3">
         <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
-        <v>9770</v>
+        <v>9617</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C40" s="4">
-        <v>57</v>
+        <v>113.7</v>
       </c>
       <c r="D40" s="3">
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
-        <v>9869</v>
+        <v>9770</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C41" s="4">
-        <v>487</v>
+        <v>57</v>
       </c>
       <c r="D41" s="3">
         <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <v>10047</v>
+        <v>9869</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C42" s="4">
-        <v>0.6</v>
+        <v>487</v>
       </c>
       <c r="D42" s="3">
         <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1429,7 +1432,7 @@
         <v>37</v>
       </c>
       <c r="C43" s="4">
-        <v>1498</v>
+        <v>0.6</v>
       </c>
       <c r="D43" s="3">
         <v>13</v>
@@ -1440,19 +1443,19 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
-        <v>10103</v>
+        <v>10047</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C44" s="4">
-        <v>50</v>
+        <v>1498</v>
       </c>
       <c r="D44" s="3">
         <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1463,41 +1466,41 @@
         <v>39</v>
       </c>
       <c r="C45" s="4">
-        <v>1026.5</v>
+        <v>50</v>
       </c>
       <c r="D45" s="3">
         <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <v>10247</v>
+        <v>10103</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C46" s="4">
-        <v>1027</v>
+        <v>1026.5</v>
       </c>
       <c r="D46" s="3">
         <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <v>10573</v>
+        <v>10247</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C47" s="4">
-        <v>232.1</v>
+        <v>1027</v>
       </c>
       <c r="D47" s="3">
         <v>13</v>
@@ -1508,36 +1511,36 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <v>10608</v>
+        <v>10573</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C48" s="4">
-        <v>100</v>
+        <v>232.1</v>
       </c>
       <c r="D48" s="3">
         <v>13</v>
       </c>
       <c r="E48" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <v>12262</v>
+        <v>10608</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C49" s="4">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D49" s="3">
         <v>13</v>
       </c>
       <c r="E49" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -1545,7 +1548,7 @@
         <v>12492</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C50" s="4">
         <v>2694.5</v>
@@ -1554,7 +1557,7 @@
         <v>13</v>
       </c>
       <c r="E50" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -1562,7 +1565,7 @@
         <v>12494</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C51" s="4">
         <v>10</v>
@@ -1571,7 +1574,7 @@
         <v>13</v>
       </c>
       <c r="E51" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -1579,7 +1582,7 @@
         <v>12494</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C52" s="4">
         <v>911</v>
@@ -1588,7 +1591,7 @@
         <v>13</v>
       </c>
       <c r="E52" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -1596,7 +1599,7 @@
         <v>12494</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C53" s="4">
         <v>1493</v>
@@ -1605,7 +1608,7 @@
         <v>13</v>
       </c>
       <c r="E53" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -1613,7 +1616,7 @@
         <v>13485</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C54" s="4">
         <v>946</v>
@@ -1622,7 +1625,7 @@
         <v>13</v>
       </c>
       <c r="E54" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -1630,7 +1633,7 @@
         <v>13486</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C55" s="4">
         <v>30</v>
@@ -1639,7 +1642,7 @@
         <v>13</v>
       </c>
       <c r="E55" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -1647,16 +1650,16 @@
         <v>13486</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C56" s="4">
-        <v>5620</v>
+        <v>3400</v>
       </c>
       <c r="D56" s="3">
         <v>13</v>
       </c>
       <c r="E56" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -1664,7 +1667,7 @@
         <v>14479</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C57" s="4">
         <v>50</v>
@@ -1673,7 +1676,7 @@
         <v>13</v>
       </c>
       <c r="E57" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -1681,7 +1684,7 @@
         <v>14479</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C58" s="4">
         <v>1103.5</v>
@@ -1690,7 +1693,7 @@
         <v>13</v>
       </c>
       <c r="E58" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -1698,7 +1701,7 @@
         <v>14479</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C59" s="4">
         <v>12320</v>
@@ -1707,41 +1710,41 @@
         <v>13</v>
       </c>
       <c r="E59" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <v>14730</v>
+        <v>16048</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C60" s="4">
-        <v>670</v>
+        <v>3017</v>
       </c>
       <c r="D60" s="3">
         <v>13</v>
       </c>
       <c r="E60" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <v>16048</v>
+        <v>16904</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C61" s="4">
-        <v>3017</v>
+        <v>4014</v>
       </c>
       <c r="D61" s="3">
         <v>13</v>
       </c>
       <c r="E61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -1749,16 +1752,16 @@
         <v>16904</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C62" s="4">
-        <v>5734</v>
+        <v>21633</v>
       </c>
       <c r="D62" s="3">
         <v>13</v>
       </c>
       <c r="E62" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -1766,16 +1769,16 @@
         <v>16905</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C63" s="4">
-        <v>1415</v>
+        <v>855</v>
       </c>
       <c r="D63" s="3">
         <v>13</v>
       </c>
       <c r="E63" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -1783,16 +1786,16 @@
         <v>17065</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C64" s="4">
-        <v>4730</v>
+        <v>2930</v>
       </c>
       <c r="D64" s="3">
         <v>13</v>
       </c>
       <c r="E64" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -1800,7 +1803,7 @@
         <v>17611</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C65" s="4">
         <v>190</v>
@@ -1809,7 +1812,7 @@
         <v>13</v>
       </c>
       <c r="E65" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -1817,7 +1820,7 @@
         <v>17612</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C66" s="4">
         <v>40</v>
@@ -1826,7 +1829,7 @@
         <v>13</v>
       </c>
       <c r="E66" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -1834,7 +1837,7 @@
         <v>17929</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C67" s="4">
         <v>10053</v>
@@ -1843,58 +1846,58 @@
         <v>13</v>
       </c>
       <c r="E67" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
-        <v>30099</v>
+        <v>18074</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="C68" s="4">
-        <v>4737</v>
+        <v>9649</v>
       </c>
       <c r="D68" s="3">
         <v>13</v>
       </c>
       <c r="E68" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
-        <v>30100</v>
+        <v>18123</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C69" s="4">
-        <v>30</v>
+        <v>2000</v>
       </c>
       <c r="D69" s="3">
         <v>13</v>
       </c>
       <c r="E69" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
-        <v>30100</v>
+        <v>30099</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C70" s="4">
-        <v>1520</v>
+        <v>14424</v>
       </c>
       <c r="D70" s="3">
         <v>13</v>
       </c>
       <c r="E70" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -1902,50 +1905,50 @@
         <v>30100</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C71" s="4">
-        <v>3513</v>
+        <v>30</v>
       </c>
       <c r="D71" s="3">
         <v>13</v>
       </c>
       <c r="E71" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
-        <v>30101</v>
+        <v>30100</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C72" s="4">
-        <v>30</v>
+        <v>1520</v>
       </c>
       <c r="D72" s="3">
         <v>13</v>
       </c>
       <c r="E72" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
-        <v>30101</v>
+        <v>30100</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C73" s="4">
-        <v>342</v>
+        <v>2913</v>
       </c>
       <c r="D73" s="3">
         <v>13</v>
       </c>
       <c r="E73" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -1953,58 +1956,58 @@
         <v>30101</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C74" s="4">
-        <v>3802</v>
+        <v>30</v>
       </c>
       <c r="D74" s="3">
         <v>13</v>
       </c>
       <c r="E74" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <v>30102</v>
+        <v>30101</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C75" s="4">
-        <v>30</v>
+        <v>342</v>
       </c>
       <c r="D75" s="3">
         <v>13</v>
       </c>
       <c r="E75" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <v>30102</v>
+        <v>30101</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C76" s="4">
-        <v>715</v>
+        <v>3802</v>
       </c>
       <c r="D76" s="3">
         <v>13</v>
       </c>
       <c r="E76" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <v>30103</v>
+        <v>30102</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C77" s="4">
         <v>30</v>
@@ -2013,24 +2016,24 @@
         <v>13</v>
       </c>
       <c r="E77" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <v>30103</v>
+        <v>30102</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C78" s="4">
-        <v>162</v>
+        <v>715</v>
       </c>
       <c r="D78" s="3">
         <v>13</v>
       </c>
       <c r="E78" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -2038,50 +2041,50 @@
         <v>30103</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C79" s="4">
-        <v>3395</v>
+        <v>30</v>
       </c>
       <c r="D79" s="3">
         <v>13</v>
       </c>
       <c r="E79" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <v>30104</v>
+        <v>30103</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C80" s="4">
-        <v>30</v>
+        <v>212</v>
       </c>
       <c r="D80" s="3">
         <v>13</v>
       </c>
       <c r="E80" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <v>30104</v>
+        <v>30103</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C81" s="4">
-        <v>1830</v>
+        <v>2345</v>
       </c>
       <c r="D81" s="3">
         <v>13</v>
       </c>
       <c r="E81" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -2089,58 +2092,58 @@
         <v>30104</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C82" s="4">
-        <v>7767</v>
+        <v>30</v>
       </c>
       <c r="D82" s="3">
         <v>13</v>
       </c>
       <c r="E82" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
-        <v>30105</v>
+        <v>30104</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C83" s="4">
-        <v>30</v>
+        <v>1830</v>
       </c>
       <c r="D83" s="3">
         <v>13</v>
       </c>
       <c r="E83" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
-        <v>30105</v>
+        <v>30104</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C84" s="4">
-        <v>1171</v>
+        <v>7767</v>
       </c>
       <c r="D84" s="3">
         <v>13</v>
       </c>
       <c r="E84" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
-        <v>30106</v>
+        <v>30105</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C85" s="4">
         <v>30</v>
@@ -2149,24 +2152,24 @@
         <v>13</v>
       </c>
       <c r="E85" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
-        <v>30106</v>
+        <v>30105</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C86" s="4">
-        <v>1500</v>
+        <v>3548</v>
       </c>
       <c r="D86" s="3">
         <v>13</v>
       </c>
       <c r="E86" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -2174,58 +2177,58 @@
         <v>30106</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C87" s="4">
-        <v>3875</v>
+        <v>30</v>
       </c>
       <c r="D87" s="3">
         <v>13</v>
       </c>
       <c r="E87" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
-        <v>30107</v>
+        <v>30106</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C88" s="4">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="D88" s="3">
         <v>13</v>
       </c>
       <c r="E88" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <v>30107</v>
+        <v>30106</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C89" s="4">
-        <v>1252</v>
+        <v>3875</v>
       </c>
       <c r="D89" s="3">
         <v>13</v>
       </c>
       <c r="E89" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <v>30108</v>
+        <v>30107</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C90" s="4">
         <v>30</v>
@@ -2234,24 +2237,24 @@
         <v>13</v>
       </c>
       <c r="E90" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
-        <v>30108</v>
+        <v>30107</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C91" s="4">
-        <v>120</v>
+        <v>1137</v>
       </c>
       <c r="D91" s="3">
         <v>13</v>
       </c>
       <c r="E91" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -2259,50 +2262,50 @@
         <v>30108</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C92" s="4">
-        <v>3904</v>
+        <v>30</v>
       </c>
       <c r="D92" s="3">
         <v>13</v>
       </c>
       <c r="E92" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
-        <v>30109</v>
+        <v>30108</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C93" s="4">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D93" s="3">
         <v>13</v>
       </c>
       <c r="E93" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
-        <v>30109</v>
+        <v>30108</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C94" s="4">
-        <v>90</v>
+        <v>3904</v>
       </c>
       <c r="D94" s="3">
         <v>13</v>
       </c>
       <c r="E94" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -2310,50 +2313,50 @@
         <v>30109</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C95" s="4">
-        <v>5932</v>
+        <v>30</v>
       </c>
       <c r="D95" s="3">
         <v>13</v>
       </c>
       <c r="E95" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
-        <v>30110</v>
+        <v>30109</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C96" s="4">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="D96" s="3">
         <v>13</v>
       </c>
       <c r="E96" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
-        <v>30110</v>
+        <v>30109</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C97" s="4">
-        <v>2787</v>
+        <v>5932</v>
       </c>
       <c r="D97" s="3">
         <v>13</v>
       </c>
       <c r="E97" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
@@ -2361,50 +2364,50 @@
         <v>30110</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C98" s="4">
-        <v>3540</v>
+        <v>30</v>
       </c>
       <c r="D98" s="3">
         <v>13</v>
       </c>
       <c r="E98" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
-        <v>30111</v>
+        <v>30110</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C99" s="4">
-        <v>30</v>
+        <v>2787</v>
       </c>
       <c r="D99" s="3">
         <v>13</v>
       </c>
       <c r="E99" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
-        <v>30111</v>
+        <v>30110</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C100" s="4">
-        <v>2370</v>
+        <v>3540</v>
       </c>
       <c r="D100" s="3">
         <v>13</v>
       </c>
       <c r="E100" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -2412,50 +2415,50 @@
         <v>30111</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C101" s="4">
-        <v>7781</v>
+        <v>30</v>
       </c>
       <c r="D101" s="3">
         <v>13</v>
       </c>
       <c r="E101" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
-        <v>30113</v>
+        <v>30111</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C102" s="4">
-        <v>30</v>
+        <v>2370</v>
       </c>
       <c r="D102" s="3">
         <v>13</v>
       </c>
       <c r="E102" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
-        <v>30113</v>
+        <v>30111</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C103" s="4">
-        <v>830</v>
+        <v>7781</v>
       </c>
       <c r="D103" s="3">
         <v>13</v>
       </c>
       <c r="E103" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -2463,50 +2466,50 @@
         <v>30113</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C104" s="4">
-        <v>3431</v>
+        <v>30</v>
       </c>
       <c r="D104" s="3">
         <v>13</v>
       </c>
       <c r="E104" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
-        <v>30117</v>
+        <v>30113</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C105" s="4">
-        <v>30</v>
+        <v>830</v>
       </c>
       <c r="D105" s="3">
         <v>13</v>
       </c>
       <c r="E105" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
-        <v>30117</v>
+        <v>30113</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C106" s="4">
-        <v>2815</v>
+        <v>3431</v>
       </c>
       <c r="D106" s="3">
         <v>13</v>
       </c>
       <c r="E106" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
@@ -2514,50 +2517,50 @@
         <v>30117</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C107" s="4">
-        <v>4951</v>
+        <v>30</v>
       </c>
       <c r="D107" s="3">
         <v>13</v>
       </c>
       <c r="E107" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
-        <v>30118</v>
+        <v>30117</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C108" s="4">
-        <v>30</v>
+        <v>4951</v>
       </c>
       <c r="D108" s="3">
         <v>13</v>
       </c>
       <c r="E108" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
-        <v>30118</v>
+        <v>30117</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C109" s="4">
-        <v>2246</v>
+        <v>9913</v>
       </c>
       <c r="D109" s="3">
         <v>13</v>
       </c>
       <c r="E109" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
@@ -2565,58 +2568,68 @@
         <v>30118</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C110" s="4">
-        <v>2840</v>
+        <v>30</v>
       </c>
       <c r="D110" s="3">
         <v>13</v>
       </c>
       <c r="E110" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
-        <v>30169</v>
+        <v>30118</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C111" s="4">
-        <v>50</v>
+        <v>2246</v>
       </c>
       <c r="D111" s="3">
         <v>13</v>
       </c>
       <c r="E111" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
-        <v>30215</v>
+        <v>30118</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C112" s="4">
+        <v>2840</v>
+      </c>
+      <c r="D112" s="3">
+        <v>13</v>
+      </c>
+      <c r="E112" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="3">
+        <v>30169</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C113" s="4">
         <v>50</v>
       </c>
-      <c r="D112" s="3">
-        <v>13</v>
-      </c>
-      <c r="E112" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="3"/>
-      <c r="B113" s="1"/>
-      <c r="C113" s="4"/>
-      <c r="D113" s="3"/>
-      <c r="E113" s="1"/>
+      <c r="D113" s="3">
+        <v>13</v>
+      </c>
+      <c r="E113" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="3"/>

--- a/data-source/ESTOQUEBASESLOCAL.xlsx
+++ b/data-source/ESTOQUEBASESLOCAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{623C5EE9-E726-4051-8B3C-7C3F13BD1A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA7D2625-C1D3-4A59-B542-289C19B43653}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{623C5EE9-E726-4051-8B3C-7C3F13BD1A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6275EAD9-E33D-4E89-848E-342332DCA11D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="84">
   <si>
     <t>Produto</t>
   </si>
@@ -289,9 +289,6 @@
   </si>
   <si>
     <t>NAPA TURIM 1.0 BRANCO 99- BEIRA RIO</t>
-  </si>
-  <si>
-    <t>BASE PEQUIM PU 1.0MM - BEGE 626</t>
   </si>
 </sst>
 </file>
@@ -378,6 +375,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -707,7 +708,7 @@
     <col min="2" max="2" width="54.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -769,7 +770,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="4">
-        <v>6</v>
+        <v>2848</v>
       </c>
       <c r="D4" s="3">
         <v>13</v>
@@ -780,13 +781,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>6518</v>
+        <v>6520</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="4">
-        <v>2842</v>
+        <v>1700</v>
       </c>
       <c r="D5" s="3">
         <v>13</v>
@@ -797,36 +798,36 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>6520</v>
+        <v>6594</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4">
-        <v>1700</v>
+        <v>192</v>
       </c>
       <c r="D6" s="3">
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>6594</v>
+        <v>8007</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="4">
-        <v>192</v>
+        <v>100</v>
       </c>
       <c r="D7" s="3">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -837,7 +838,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="4">
-        <v>100</v>
+        <v>188</v>
       </c>
       <c r="D8" s="3">
         <v>13</v>
@@ -848,36 +849,36 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>8007</v>
+        <v>8875</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="4">
-        <v>188</v>
+        <v>359.6</v>
       </c>
       <c r="D9" s="3">
         <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>8875</v>
+        <v>8879</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C10" s="4">
-        <v>359.6</v>
+        <v>76.5</v>
       </c>
       <c r="D10" s="3">
         <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -888,7 +889,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="4">
-        <v>76.5</v>
+        <v>364</v>
       </c>
       <c r="D11" s="3">
         <v>13</v>
@@ -899,13 +900,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <v>8879</v>
+        <v>8881</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="4">
-        <v>364</v>
+        <v>18.7</v>
       </c>
       <c r="D12" s="3">
         <v>13</v>
@@ -922,7 +923,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="4">
-        <v>18.7</v>
+        <v>1077</v>
       </c>
       <c r="D13" s="3">
         <v>13</v>
@@ -933,13 +934,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>8881</v>
+        <v>8882</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" s="4">
-        <v>1077</v>
+        <v>3.2</v>
       </c>
       <c r="D14" s="3">
         <v>13</v>
@@ -956,7 +957,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="4">
-        <v>3.2</v>
+        <v>1240</v>
       </c>
       <c r="D15" s="3">
         <v>13</v>
@@ -967,30 +968,30 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>8882</v>
+        <v>8923</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="C16" s="4">
-        <v>1240</v>
+        <v>1160</v>
       </c>
       <c r="D16" s="3">
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>8923</v>
+        <v>8924</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C17" s="4">
-        <v>1160</v>
+        <v>1012</v>
       </c>
       <c r="D17" s="3">
         <v>13</v>
@@ -1001,47 +1002,47 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>8924</v>
+        <v>8926</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="C18" s="4">
-        <v>1012</v>
+        <v>3662</v>
       </c>
       <c r="D18" s="3">
         <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>8926</v>
+        <v>9004</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C19" s="4">
-        <v>3662</v>
+        <v>195</v>
       </c>
       <c r="D19" s="3">
         <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>9004</v>
+        <v>9010</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20" s="4">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D20" s="3">
         <v>13</v>
@@ -1052,13 +1053,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>9010</v>
+        <v>9073</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C21" s="4">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D21" s="3">
         <v>13</v>
@@ -1069,19 +1070,19 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>9073</v>
+        <v>9091</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C22" s="4">
-        <v>194</v>
+        <v>11730</v>
       </c>
       <c r="D22" s="3">
         <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1092,7 +1093,7 @@
         <v>23</v>
       </c>
       <c r="C23" s="4">
-        <v>11730</v>
+        <v>23983.5</v>
       </c>
       <c r="D23" s="3">
         <v>13</v>
@@ -1103,47 +1104,47 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>9091</v>
+        <v>9297</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C24" s="4">
-        <v>26223.5</v>
+        <v>100</v>
       </c>
       <c r="D24" s="3">
         <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>9297</v>
+        <v>9298</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C25" s="4">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="D25" s="3">
         <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <v>9298</v>
+        <v>9300</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C26" s="4">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="D26" s="3">
         <v>13</v>
@@ -1154,19 +1155,19 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>9300</v>
+        <v>9468</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" s="4">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D27" s="3">
         <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1177,7 +1178,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="4">
-        <v>50</v>
+        <v>275</v>
       </c>
       <c r="D28" s="3">
         <v>13</v>
@@ -1188,13 +1189,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <v>9468</v>
+        <v>9469</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C29" s="4">
-        <v>275</v>
+        <v>49.7</v>
       </c>
       <c r="D29" s="3">
         <v>13</v>
@@ -1211,7 +1212,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="4">
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="D30" s="3">
         <v>13</v>
@@ -1228,7 +1229,7 @@
         <v>28</v>
       </c>
       <c r="C31" s="4">
-        <v>50</v>
+        <v>473</v>
       </c>
       <c r="D31" s="3">
         <v>13</v>
@@ -1239,19 +1240,19 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
-        <v>9469</v>
+        <v>9573</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C32" s="4">
-        <v>473</v>
+        <v>20.5</v>
       </c>
       <c r="D32" s="3">
         <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1262,7 +1263,7 @@
         <v>29</v>
       </c>
       <c r="C33" s="4">
-        <v>20.5</v>
+        <v>440</v>
       </c>
       <c r="D33" s="3">
         <v>13</v>
@@ -1273,36 +1274,36 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
-        <v>9573</v>
+        <v>9614</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C34" s="4">
-        <v>440</v>
+        <v>3050.5</v>
       </c>
       <c r="D34" s="3">
         <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <v>9614</v>
+        <v>9615</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C35" s="4">
-        <v>3050.5</v>
+        <v>50</v>
       </c>
       <c r="D35" s="3">
         <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1313,7 +1314,7 @@
         <v>32</v>
       </c>
       <c r="C36" s="4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D36" s="3">
         <v>13</v>
@@ -1324,13 +1325,13 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
-        <v>9615</v>
+        <v>9616</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C37" s="4">
-        <v>60</v>
+        <v>309.3</v>
       </c>
       <c r="D37" s="3">
         <v>13</v>
@@ -1341,13 +1342,13 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
-        <v>9616</v>
+        <v>9617</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C38" s="4">
-        <v>309.3</v>
+        <v>50</v>
       </c>
       <c r="D38" s="3">
         <v>13</v>
@@ -1364,7 +1365,7 @@
         <v>34</v>
       </c>
       <c r="C39" s="4">
-        <v>50</v>
+        <v>113.7</v>
       </c>
       <c r="D39" s="3">
         <v>13</v>
@@ -1375,13 +1376,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
-        <v>9617</v>
+        <v>9770</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C40" s="4">
-        <v>113.7</v>
+        <v>57</v>
       </c>
       <c r="D40" s="3">
         <v>13</v>
@@ -1392,36 +1393,36 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
-        <v>9770</v>
+        <v>9869</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C41" s="4">
-        <v>57</v>
+        <v>487</v>
       </c>
       <c r="D41" s="3">
         <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <v>9869</v>
+        <v>10047</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C42" s="4">
-        <v>487</v>
+        <v>0.6</v>
       </c>
       <c r="D42" s="3">
         <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1432,7 +1433,7 @@
         <v>37</v>
       </c>
       <c r="C43" s="4">
-        <v>0.6</v>
+        <v>1498</v>
       </c>
       <c r="D43" s="3">
         <v>13</v>
@@ -1443,19 +1444,19 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
-        <v>10047</v>
+        <v>10103</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C44" s="4">
-        <v>1498</v>
+        <v>50</v>
       </c>
       <c r="D44" s="3">
         <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1466,7 +1467,7 @@
         <v>39</v>
       </c>
       <c r="C45" s="4">
-        <v>50</v>
+        <v>1026.5</v>
       </c>
       <c r="D45" s="3">
         <v>13</v>
@@ -1477,30 +1478,30 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <v>10103</v>
+        <v>10247</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C46" s="4">
-        <v>1026.5</v>
+        <v>1027</v>
       </c>
       <c r="D46" s="3">
         <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <v>10247</v>
+        <v>10573</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C47" s="4">
-        <v>1027</v>
+        <v>232.1</v>
       </c>
       <c r="D47" s="3">
         <v>13</v>
@@ -1511,47 +1512,47 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <v>10573</v>
+        <v>10608</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C48" s="4">
-        <v>232.1</v>
+        <v>100</v>
       </c>
       <c r="D48" s="3">
         <v>13</v>
       </c>
       <c r="E48" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <v>10608</v>
+        <v>12492</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C49" s="4">
-        <v>100</v>
+        <v>2694.5</v>
       </c>
       <c r="D49" s="3">
         <v>13</v>
       </c>
       <c r="E49" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
-        <v>12492</v>
+        <v>12494</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C50" s="4">
-        <v>2694.5</v>
+        <v>10</v>
       </c>
       <c r="D50" s="3">
         <v>13</v>
@@ -1568,7 +1569,7 @@
         <v>46</v>
       </c>
       <c r="C51" s="4">
-        <v>10</v>
+        <v>911</v>
       </c>
       <c r="D51" s="3">
         <v>13</v>
@@ -1585,7 +1586,7 @@
         <v>46</v>
       </c>
       <c r="C52" s="4">
-        <v>911</v>
+        <v>1493</v>
       </c>
       <c r="D52" s="3">
         <v>13</v>
@@ -1596,30 +1597,30 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <v>12494</v>
+        <v>13485</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C53" s="4">
-        <v>1493</v>
+        <v>646</v>
       </c>
       <c r="D53" s="3">
         <v>13</v>
       </c>
       <c r="E53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
-        <v>13485</v>
+        <v>13486</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C54" s="4">
-        <v>946</v>
+        <v>30</v>
       </c>
       <c r="D54" s="3">
         <v>13</v>
@@ -1636,7 +1637,7 @@
         <v>44</v>
       </c>
       <c r="C55" s="4">
-        <v>30</v>
+        <v>3000</v>
       </c>
       <c r="D55" s="3">
         <v>13</v>
@@ -1647,19 +1648,19 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
-        <v>13486</v>
+        <v>14479</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C56" s="4">
-        <v>3400</v>
+        <v>50</v>
       </c>
       <c r="D56" s="3">
         <v>13</v>
       </c>
       <c r="E56" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -1670,7 +1671,7 @@
         <v>47</v>
       </c>
       <c r="C57" s="4">
-        <v>50</v>
+        <v>668.5</v>
       </c>
       <c r="D57" s="3">
         <v>13</v>
@@ -1687,7 +1688,7 @@
         <v>47</v>
       </c>
       <c r="C58" s="4">
-        <v>1103.5</v>
+        <v>12320</v>
       </c>
       <c r="D58" s="3">
         <v>13</v>
@@ -1698,13 +1699,13 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
-        <v>14479</v>
+        <v>16048</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C59" s="4">
-        <v>12320</v>
+        <v>3017</v>
       </c>
       <c r="D59" s="3">
         <v>13</v>
@@ -1715,30 +1716,30 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <v>16048</v>
+        <v>16904</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C60" s="4">
-        <v>3017</v>
+        <v>24217</v>
       </c>
       <c r="D60" s="3">
         <v>13</v>
       </c>
       <c r="E60" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <v>16904</v>
+        <v>16905</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C61" s="4">
-        <v>4014</v>
+        <v>655</v>
       </c>
       <c r="D61" s="3">
         <v>13</v>
@@ -1749,149 +1750,149 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <v>16904</v>
+        <v>17065</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C62" s="4">
-        <v>21633</v>
+        <v>1402</v>
       </c>
       <c r="D62" s="3">
         <v>13</v>
       </c>
       <c r="E62" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
-        <v>16905</v>
+        <v>17611</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C63" s="4">
-        <v>855</v>
+        <v>190</v>
       </c>
       <c r="D63" s="3">
         <v>13</v>
       </c>
       <c r="E63" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
-        <v>17065</v>
+        <v>17612</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C64" s="4">
-        <v>2930</v>
+        <v>40</v>
       </c>
       <c r="D64" s="3">
         <v>13</v>
       </c>
       <c r="E64" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
-        <v>17611</v>
+        <v>17929</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="C65" s="4">
-        <v>190</v>
+        <v>9538</v>
       </c>
       <c r="D65" s="3">
         <v>13</v>
       </c>
       <c r="E65" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
-        <v>17612</v>
+        <v>18074</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="C66" s="4">
-        <v>40</v>
+        <v>4599</v>
       </c>
       <c r="D66" s="3">
         <v>13</v>
       </c>
       <c r="E66" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
-        <v>17929</v>
+        <v>18123</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C67" s="4">
-        <v>10053</v>
+        <v>1400</v>
       </c>
       <c r="D67" s="3">
         <v>13</v>
       </c>
       <c r="E67" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
-        <v>18074</v>
+        <v>30099</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="C68" s="4">
-        <v>9649</v>
+        <v>4844</v>
       </c>
       <c r="D68" s="3">
         <v>13</v>
       </c>
       <c r="E68" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
-        <v>18123</v>
+        <v>30100</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="C69" s="4">
-        <v>2000</v>
+        <v>1520</v>
       </c>
       <c r="D69" s="3">
         <v>13</v>
       </c>
       <c r="E69" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
-        <v>30099</v>
+        <v>30100</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C70" s="4">
-        <v>14424</v>
+        <v>2913</v>
       </c>
       <c r="D70" s="3">
         <v>13</v>
@@ -1902,13 +1903,13 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
-        <v>30100</v>
+        <v>30101</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C71" s="4">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="D71" s="3">
         <v>13</v>
@@ -1919,13 +1920,13 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
-        <v>30100</v>
+        <v>30101</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C72" s="4">
-        <v>1520</v>
+        <v>3802</v>
       </c>
       <c r="D72" s="3">
         <v>13</v>
@@ -1936,13 +1937,13 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
-        <v>30100</v>
+        <v>30102</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C73" s="4">
-        <v>2913</v>
+        <v>715</v>
       </c>
       <c r="D73" s="3">
         <v>13</v>
@@ -1953,13 +1954,13 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
-        <v>30101</v>
+        <v>30103</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C74" s="4">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D74" s="3">
         <v>13</v>
@@ -1970,13 +1971,13 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <v>30101</v>
+        <v>30103</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C75" s="4">
-        <v>342</v>
+        <v>2345</v>
       </c>
       <c r="D75" s="3">
         <v>13</v>
@@ -1987,13 +1988,13 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <v>30101</v>
+        <v>30104</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C76" s="4">
-        <v>3802</v>
+        <v>376</v>
       </c>
       <c r="D76" s="3">
         <v>13</v>
@@ -2004,13 +2005,13 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <v>30102</v>
+        <v>30104</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C77" s="4">
-        <v>30</v>
+        <v>7767</v>
       </c>
       <c r="D77" s="3">
         <v>13</v>
@@ -2021,13 +2022,13 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <v>30102</v>
+        <v>30105</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C78" s="4">
-        <v>715</v>
+        <v>3548</v>
       </c>
       <c r="D78" s="3">
         <v>13</v>
@@ -2038,13 +2039,13 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
-        <v>30103</v>
+        <v>30106</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C79" s="4">
-        <v>30</v>
+        <v>3875</v>
       </c>
       <c r="D79" s="3">
         <v>13</v>
@@ -2055,13 +2056,13 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <v>30103</v>
+        <v>30107</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C80" s="4">
-        <v>212</v>
+        <v>1037</v>
       </c>
       <c r="D80" s="3">
         <v>13</v>
@@ -2072,13 +2073,13 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <v>30103</v>
+        <v>30108</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C81" s="4">
-        <v>2345</v>
+        <v>120</v>
       </c>
       <c r="D81" s="3">
         <v>13</v>
@@ -2089,13 +2090,13 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
-        <v>30104</v>
+        <v>30108</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C82" s="4">
-        <v>30</v>
+        <v>3904</v>
       </c>
       <c r="D82" s="3">
         <v>13</v>
@@ -2106,13 +2107,13 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
-        <v>30104</v>
+        <v>30109</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C83" s="4">
-        <v>1830</v>
+        <v>90</v>
       </c>
       <c r="D83" s="3">
         <v>13</v>
@@ -2123,13 +2124,13 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
-        <v>30104</v>
+        <v>30109</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C84" s="4">
-        <v>7767</v>
+        <v>5932</v>
       </c>
       <c r="D84" s="3">
         <v>13</v>
@@ -2140,13 +2141,13 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
-        <v>30105</v>
+        <v>30110</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C85" s="4">
-        <v>30</v>
+        <v>2687</v>
       </c>
       <c r="D85" s="3">
         <v>13</v>
@@ -2157,13 +2158,13 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
-        <v>30105</v>
+        <v>30110</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C86" s="4">
-        <v>3548</v>
+        <v>3540</v>
       </c>
       <c r="D86" s="3">
         <v>13</v>
@@ -2174,13 +2175,13 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
-        <v>30106</v>
+        <v>30111</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C87" s="4">
-        <v>30</v>
+        <v>2370</v>
       </c>
       <c r="D87" s="3">
         <v>13</v>
@@ -2191,13 +2192,13 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
-        <v>30106</v>
+        <v>30111</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C88" s="4">
-        <v>1000</v>
+        <v>7781</v>
       </c>
       <c r="D88" s="3">
         <v>13</v>
@@ -2208,13 +2209,13 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C89" s="4">
-        <v>3875</v>
+        <v>830</v>
       </c>
       <c r="D89" s="3">
         <v>13</v>
@@ -2225,13 +2226,13 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <v>30107</v>
+        <v>30113</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C90" s="4">
-        <v>30</v>
+        <v>3381</v>
       </c>
       <c r="D90" s="3">
         <v>13</v>
@@ -2242,13 +2243,13 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
-        <v>30107</v>
+        <v>30117</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C91" s="4">
-        <v>1137</v>
+        <v>4951</v>
       </c>
       <c r="D91" s="3">
         <v>13</v>
@@ -2259,13 +2260,13 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
-        <v>30108</v>
+        <v>30117</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C92" s="4">
-        <v>30</v>
+        <v>9813</v>
       </c>
       <c r="D92" s="3">
         <v>13</v>
@@ -2276,13 +2277,13 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
-        <v>30108</v>
+        <v>30118</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C93" s="4">
-        <v>120</v>
+        <v>2246</v>
       </c>
       <c r="D93" s="3">
         <v>13</v>
@@ -2293,13 +2294,13 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
-        <v>30108</v>
+        <v>30118</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C94" s="4">
-        <v>3904</v>
+        <v>2840</v>
       </c>
       <c r="D94" s="3">
         <v>13</v>
@@ -2309,327 +2310,118 @@
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="3">
-        <v>30109</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C95" s="4">
-        <v>30</v>
-      </c>
-      <c r="D95" s="3">
-        <v>13</v>
-      </c>
-      <c r="E95" t="s">
-        <v>73</v>
-      </c>
+      <c r="A95" s="3"/>
+      <c r="B95" s="1"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="3"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="3">
-        <v>30109</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C96" s="4">
-        <v>90</v>
-      </c>
-      <c r="D96" s="3">
-        <v>13</v>
-      </c>
-      <c r="E96" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="3">
-        <v>30109</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C97" s="4">
-        <v>5932</v>
-      </c>
-      <c r="D97" s="3">
-        <v>13</v>
-      </c>
-      <c r="E97" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="3">
-        <v>30110</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C98" s="4">
-        <v>30</v>
-      </c>
-      <c r="D98" s="3">
-        <v>13</v>
-      </c>
-      <c r="E98" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="3">
-        <v>30110</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C99" s="4">
-        <v>2787</v>
-      </c>
-      <c r="D99" s="3">
-        <v>13</v>
-      </c>
-      <c r="E99" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="3">
-        <v>30110</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C100" s="4">
-        <v>3540</v>
-      </c>
-      <c r="D100" s="3">
-        <v>13</v>
-      </c>
-      <c r="E100" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" s="3">
-        <v>30111</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C101" s="4">
-        <v>30</v>
-      </c>
-      <c r="D101" s="3">
-        <v>13</v>
-      </c>
-      <c r="E101" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" s="3">
-        <v>30111</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C102" s="4">
-        <v>2370</v>
-      </c>
-      <c r="D102" s="3">
-        <v>13</v>
-      </c>
-      <c r="E102" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="3">
-        <v>30111</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C103" s="4">
-        <v>7781</v>
-      </c>
-      <c r="D103" s="3">
-        <v>13</v>
-      </c>
-      <c r="E103" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="3">
-        <v>30113</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C104" s="4">
-        <v>30</v>
-      </c>
-      <c r="D104" s="3">
-        <v>13</v>
-      </c>
-      <c r="E104" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" s="3">
-        <v>30113</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C105" s="4">
-        <v>830</v>
-      </c>
-      <c r="D105" s="3">
-        <v>13</v>
-      </c>
-      <c r="E105" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" s="3">
-        <v>30113</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C106" s="4">
-        <v>3431</v>
-      </c>
-      <c r="D106" s="3">
-        <v>13</v>
-      </c>
-      <c r="E106" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="3">
-        <v>30117</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C107" s="4">
-        <v>30</v>
-      </c>
-      <c r="D107" s="3">
-        <v>13</v>
-      </c>
-      <c r="E107" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="3">
-        <v>30117</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C108" s="4">
-        <v>4951</v>
-      </c>
-      <c r="D108" s="3">
-        <v>13</v>
-      </c>
-      <c r="E108" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="3">
-        <v>30117</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C109" s="4">
-        <v>9913</v>
-      </c>
-      <c r="D109" s="3">
-        <v>13</v>
-      </c>
-      <c r="E109" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" s="3">
-        <v>30118</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C110" s="4">
-        <v>30</v>
-      </c>
-      <c r="D110" s="3">
-        <v>13</v>
-      </c>
-      <c r="E110" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" s="3">
-        <v>30118</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C111" s="4">
-        <v>2246</v>
-      </c>
-      <c r="D111" s="3">
-        <v>13</v>
-      </c>
-      <c r="E111" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="3">
-        <v>30118</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C112" s="4">
-        <v>2840</v>
-      </c>
-      <c r="D112" s="3">
-        <v>13</v>
-      </c>
-      <c r="E112" t="s">
-        <v>73</v>
-      </c>
+      <c r="A96" s="3"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="3"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="3"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="3"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="3"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="3"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="3"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="3"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="3"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="3"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="3"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="3"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="3"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="3"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" s="3"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="3"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="3"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="3"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="3"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="4"/>
+      <c r="D105" s="3"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="3"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="3"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="3"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="3"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="3"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="4"/>
+      <c r="D108" s="3"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" s="3"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="3"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="3"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="4"/>
+      <c r="D110" s="3"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="3"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="4"/>
+      <c r="D111" s="3"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="3"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="4"/>
+      <c r="D112" s="3"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="3">
-        <v>30169</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C113" s="4">
-        <v>50</v>
-      </c>
-      <c r="D113" s="3">
-        <v>13</v>
-      </c>
-      <c r="E113" t="s">
-        <v>74</v>
-      </c>
+      <c r="A113" s="3"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="4"/>
+      <c r="D113" s="3"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="3"/>

--- a/data-source/ESTOQUEBASESLOCAL.xlsx
+++ b/data-source/ESTOQUEBASESLOCAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{623C5EE9-E726-4051-8B3C-7C3F13BD1A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6275EAD9-E33D-4E89-848E-342332DCA11D}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{623C5EE9-E726-4051-8B3C-7C3F13BD1A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F37833D-79CD-4EDE-A3E4-02BAB5E392B9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="85">
   <si>
     <t>Produto</t>
   </si>
@@ -195,9 +195,6 @@
     <t>BASE SHENZHEN PU 1,05MM BEGE</t>
   </si>
   <si>
-    <t>BASE STRETCH 0,85 - NEGRO</t>
-  </si>
-  <si>
     <t>BASE STRETCH 0,85 - BISCOITO</t>
   </si>
   <si>
@@ -289,6 +286,12 @@
   </si>
   <si>
     <t>NAPA TURIM 1.0 BRANCO 99- BEIRA RIO</t>
+  </si>
+  <si>
+    <t>BASE FLEX BRANCO 1.0</t>
+  </si>
+  <si>
+    <t>BASE SHANGHAI PU 1.05 - OCRE (COM MARCA D'AGUA)</t>
   </si>
 </sst>
 </file>
@@ -312,6 +315,7 @@
       <sz val="11"/>
       <color rgb="FF800000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -375,10 +379,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -730,19 +730,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>5323</v>
+        <v>655</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="C2" s="4">
-        <v>2</v>
+        <v>2006</v>
       </c>
       <c r="D2" s="3">
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -753,7 +753,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="4">
-        <v>1100</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>13</v>
@@ -764,70 +764,70 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>6518</v>
+        <v>5323</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" s="4">
-        <v>2848</v>
+        <v>1100</v>
       </c>
       <c r="D4" s="3">
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>6520</v>
+        <v>6518</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="4">
-        <v>1700</v>
+        <v>2748</v>
       </c>
       <c r="D5" s="3">
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>6594</v>
+        <v>6520</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="4">
-        <v>192</v>
+        <v>1600</v>
       </c>
       <c r="D6" s="3">
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>8007</v>
+        <v>6594</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="4">
-        <v>100</v>
+        <v>192</v>
       </c>
       <c r="D7" s="3">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -838,7 +838,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="4">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="D8" s="3">
         <v>13</v>
@@ -849,36 +849,36 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>8875</v>
+        <v>8007</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="4">
-        <v>359.6</v>
+        <v>188</v>
       </c>
       <c r="D9" s="3">
         <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>8879</v>
+        <v>8875</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10" s="4">
-        <v>76.5</v>
+        <v>359.6</v>
       </c>
       <c r="D10" s="3">
         <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -889,30 +889,30 @@
         <v>14</v>
       </c>
       <c r="C11" s="4">
-        <v>364</v>
+        <v>76.5</v>
       </c>
       <c r="D11" s="3">
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <v>8881</v>
+        <v>8879</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="4">
-        <v>18.7</v>
+        <v>364</v>
       </c>
       <c r="D12" s="3">
         <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -923,30 +923,30 @@
         <v>15</v>
       </c>
       <c r="C13" s="4">
-        <v>1077</v>
+        <v>18.7</v>
       </c>
       <c r="D13" s="3">
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>8882</v>
+        <v>8881</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" s="4">
-        <v>3.2</v>
+        <v>1077</v>
       </c>
       <c r="D14" s="3">
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -957,41 +957,41 @@
         <v>16</v>
       </c>
       <c r="C15" s="4">
-        <v>1240</v>
+        <v>3.2</v>
       </c>
       <c r="D15" s="3">
         <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>8923</v>
+        <v>8882</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="C16" s="4">
-        <v>1160</v>
+        <v>1240</v>
       </c>
       <c r="D16" s="3">
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>8924</v>
+        <v>8923</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C17" s="4">
-        <v>1012</v>
+        <v>1140</v>
       </c>
       <c r="D17" s="3">
         <v>13</v>
@@ -1002,47 +1002,47 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>8926</v>
+        <v>8924</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="C18" s="4">
-        <v>3662</v>
+        <v>1012</v>
       </c>
       <c r="D18" s="3">
         <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>9004</v>
+        <v>8926</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C19" s="4">
-        <v>195</v>
+        <v>3462</v>
       </c>
       <c r="D19" s="3">
         <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>9010</v>
+        <v>9004</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20" s="4">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D20" s="3">
         <v>13</v>
@@ -1053,13 +1053,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>9073</v>
+        <v>9010</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" s="4">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D21" s="3">
         <v>13</v>
@@ -1070,19 +1070,19 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>9091</v>
+        <v>9073</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" s="4">
-        <v>11730</v>
+        <v>194</v>
       </c>
       <c r="D22" s="3">
         <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1093,24 +1093,24 @@
         <v>23</v>
       </c>
       <c r="C23" s="4">
-        <v>23983.5</v>
+        <v>11730</v>
       </c>
       <c r="D23" s="3">
         <v>13</v>
       </c>
       <c r="E23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>9297</v>
+        <v>9091</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="4">
-        <v>100</v>
+        <v>22013.5</v>
       </c>
       <c r="D24" s="3">
         <v>13</v>
@@ -1121,30 +1121,30 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>9298</v>
+        <v>9297</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="4">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="D25" s="3">
         <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <v>9300</v>
+        <v>9298</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" s="4">
-        <v>30</v>
+        <v>137</v>
       </c>
       <c r="D26" s="3">
         <v>13</v>
@@ -1155,19 +1155,19 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>9468</v>
+        <v>9300</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" s="4">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D27" s="3">
         <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1178,7 +1178,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="4">
-        <v>275</v>
+        <v>50</v>
       </c>
       <c r="D28" s="3">
         <v>13</v>
@@ -1189,13 +1189,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <v>9469</v>
+        <v>9468</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" s="4">
-        <v>49.7</v>
+        <v>275</v>
       </c>
       <c r="D29" s="3">
         <v>13</v>
@@ -1212,7 +1212,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="4">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="D30" s="3">
         <v>13</v>
@@ -1229,7 +1229,7 @@
         <v>28</v>
       </c>
       <c r="C31" s="4">
-        <v>473</v>
+        <v>50</v>
       </c>
       <c r="D31" s="3">
         <v>13</v>
@@ -1240,19 +1240,19 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
-        <v>9573</v>
+        <v>9469</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C32" s="4">
-        <v>20.5</v>
+        <v>473</v>
       </c>
       <c r="D32" s="3">
         <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1263,7 +1263,7 @@
         <v>29</v>
       </c>
       <c r="C33" s="4">
-        <v>440</v>
+        <v>20.5</v>
       </c>
       <c r="D33" s="3">
         <v>13</v>
@@ -1274,36 +1274,36 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
-        <v>9614</v>
+        <v>9573</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C34" s="4">
-        <v>3050.5</v>
+        <v>440</v>
       </c>
       <c r="D34" s="3">
         <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <v>9615</v>
+        <v>9614</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" s="4">
-        <v>50</v>
+        <v>3050.5</v>
       </c>
       <c r="D35" s="3">
         <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1314,47 +1314,47 @@
         <v>32</v>
       </c>
       <c r="C36" s="4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D36" s="3">
         <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
-        <v>9616</v>
+        <v>9615</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C37" s="4">
-        <v>309.3</v>
+        <v>60</v>
       </c>
       <c r="D37" s="3">
         <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
-        <v>9617</v>
+        <v>9616</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C38" s="4">
-        <v>50</v>
+        <v>309.3</v>
       </c>
       <c r="D38" s="3">
         <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1365,64 +1365,64 @@
         <v>34</v>
       </c>
       <c r="C39" s="4">
-        <v>113.7</v>
+        <v>50</v>
       </c>
       <c r="D39" s="3">
         <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
-        <v>9770</v>
+        <v>9617</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C40" s="4">
-        <v>57</v>
+        <v>113.7</v>
       </c>
       <c r="D40" s="3">
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
-        <v>9869</v>
+        <v>9770</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C41" s="4">
-        <v>487</v>
+        <v>57</v>
       </c>
       <c r="D41" s="3">
         <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <v>10047</v>
+        <v>9869</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C42" s="4">
-        <v>0.6</v>
+        <v>487</v>
       </c>
       <c r="D42" s="3">
         <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1433,7 +1433,7 @@
         <v>37</v>
       </c>
       <c r="C43" s="4">
-        <v>1498</v>
+        <v>0.6</v>
       </c>
       <c r="D43" s="3">
         <v>13</v>
@@ -1444,19 +1444,19 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
-        <v>10103</v>
+        <v>10047</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C44" s="4">
-        <v>50</v>
+        <v>1498</v>
       </c>
       <c r="D44" s="3">
         <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1467,41 +1467,41 @@
         <v>39</v>
       </c>
       <c r="C45" s="4">
-        <v>1026.5</v>
+        <v>50</v>
       </c>
       <c r="D45" s="3">
         <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <v>10247</v>
+        <v>10103</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C46" s="4">
-        <v>1027</v>
+        <v>1026.5</v>
       </c>
       <c r="D46" s="3">
         <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <v>10573</v>
+        <v>10247</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C47" s="4">
-        <v>232.1</v>
+        <v>1027</v>
       </c>
       <c r="D47" s="3">
         <v>13</v>
@@ -1512,53 +1512,53 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <v>10608</v>
+        <v>10573</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C48" s="4">
-        <v>100</v>
+        <v>232.1</v>
       </c>
       <c r="D48" s="3">
         <v>13</v>
       </c>
       <c r="E48" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <v>12492</v>
+        <v>10608</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C49" s="4">
-        <v>2694.5</v>
+        <v>100</v>
       </c>
       <c r="D49" s="3">
         <v>13</v>
       </c>
       <c r="E49" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
-        <v>12494</v>
+        <v>12492</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C50" s="4">
-        <v>10</v>
+        <v>2694.5</v>
       </c>
       <c r="D50" s="3">
         <v>13</v>
       </c>
       <c r="E50" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -1569,13 +1569,13 @@
         <v>46</v>
       </c>
       <c r="C51" s="4">
-        <v>911</v>
+        <v>10</v>
       </c>
       <c r="D51" s="3">
         <v>13</v>
       </c>
       <c r="E51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -1586,24 +1586,24 @@
         <v>46</v>
       </c>
       <c r="C52" s="4">
-        <v>1493</v>
+        <v>911</v>
       </c>
       <c r="D52" s="3">
         <v>13</v>
       </c>
       <c r="E52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <v>13485</v>
+        <v>12494</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C53" s="4">
-        <v>646</v>
+        <v>1493</v>
       </c>
       <c r="D53" s="3">
         <v>13</v>
@@ -1614,19 +1614,19 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
-        <v>13486</v>
+        <v>13485</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C54" s="4">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="D54" s="3">
         <v>13</v>
       </c>
       <c r="E54" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -1637,24 +1637,24 @@
         <v>44</v>
       </c>
       <c r="C55" s="4">
-        <v>3000</v>
+        <v>30</v>
       </c>
       <c r="D55" s="3">
         <v>13</v>
       </c>
       <c r="E55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
-        <v>14479</v>
+        <v>13486</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C56" s="4">
-        <v>50</v>
+        <v>3000</v>
       </c>
       <c r="D56" s="3">
         <v>13</v>
@@ -1671,13 +1671,13 @@
         <v>47</v>
       </c>
       <c r="C57" s="4">
-        <v>668.5</v>
+        <v>50</v>
       </c>
       <c r="D57" s="3">
         <v>13</v>
       </c>
       <c r="E57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -1688,98 +1688,98 @@
         <v>47</v>
       </c>
       <c r="C58" s="4">
-        <v>12320</v>
+        <v>668.5</v>
       </c>
       <c r="D58" s="3">
         <v>13</v>
       </c>
       <c r="E58" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
-        <v>16048</v>
+        <v>14479</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C59" s="4">
-        <v>3017</v>
+        <v>12320</v>
       </c>
       <c r="D59" s="3">
         <v>13</v>
       </c>
       <c r="E59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <v>16904</v>
+        <v>16048</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C60" s="4">
-        <v>24217</v>
+        <v>3017</v>
       </c>
       <c r="D60" s="3">
         <v>13</v>
       </c>
       <c r="E60" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <v>16905</v>
+        <v>16904</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C61" s="4">
-        <v>655</v>
+        <v>23817</v>
       </c>
       <c r="D61" s="3">
         <v>13</v>
       </c>
       <c r="E61" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <v>17065</v>
+        <v>16905</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C62" s="4">
-        <v>1402</v>
+        <v>625</v>
       </c>
       <c r="D62" s="3">
         <v>13</v>
       </c>
       <c r="E62" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
-        <v>17611</v>
+        <v>17065</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C63" s="4">
-        <v>190</v>
+        <v>1402</v>
       </c>
       <c r="D63" s="3">
         <v>13</v>
       </c>
       <c r="E63" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -1787,7 +1787,7 @@
         <v>17612</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C64" s="4">
         <v>40</v>
@@ -1796,7 +1796,7 @@
         <v>13</v>
       </c>
       <c r="E64" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -1804,7 +1804,7 @@
         <v>17929</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C65" s="4">
         <v>9538</v>
@@ -1813,7 +1813,7 @@
         <v>13</v>
       </c>
       <c r="E65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -1821,16 +1821,16 @@
         <v>18074</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C66" s="4">
+        <v>3549</v>
+      </c>
+      <c r="D66" s="3">
+        <v>13</v>
+      </c>
+      <c r="E66" t="s">
         <v>81</v>
-      </c>
-      <c r="C66" s="4">
-        <v>4599</v>
-      </c>
-      <c r="D66" s="3">
-        <v>13</v>
-      </c>
-      <c r="E66" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -1838,7 +1838,7 @@
         <v>18123</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C67" s="4">
         <v>1400</v>
@@ -1847,7 +1847,7 @@
         <v>13</v>
       </c>
       <c r="E67" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -1855,33 +1855,33 @@
         <v>30099</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C68" s="4">
-        <v>4844</v>
+        <v>9811</v>
       </c>
       <c r="D68" s="3">
         <v>13</v>
       </c>
       <c r="E68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
-        <v>30100</v>
+        <v>30099</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C69" s="4">
-        <v>1520</v>
+        <v>33683</v>
       </c>
       <c r="D69" s="3">
         <v>13</v>
       </c>
       <c r="E69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -1889,33 +1889,33 @@
         <v>30100</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C70" s="4">
-        <v>2913</v>
+        <v>1520</v>
       </c>
       <c r="D70" s="3">
         <v>13</v>
       </c>
       <c r="E70" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
-        <v>30101</v>
+        <v>30100</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C71" s="4">
-        <v>142</v>
+        <v>2913</v>
       </c>
       <c r="D71" s="3">
         <v>13</v>
       </c>
       <c r="E71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -1923,50 +1923,50 @@
         <v>30101</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C72" s="4">
-        <v>3802</v>
+        <v>102</v>
       </c>
       <c r="D72" s="3">
         <v>13</v>
       </c>
       <c r="E72" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
-        <v>30102</v>
+        <v>30101</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C73" s="4">
-        <v>715</v>
+        <v>3802</v>
       </c>
       <c r="D73" s="3">
         <v>13</v>
       </c>
       <c r="E73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
-        <v>30103</v>
+        <v>30102</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C74" s="4">
-        <v>112</v>
+        <v>615</v>
       </c>
       <c r="D74" s="3">
         <v>13</v>
       </c>
       <c r="E74" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -1974,33 +1974,33 @@
         <v>30103</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C75" s="4">
-        <v>2345</v>
+        <v>112</v>
       </c>
       <c r="D75" s="3">
         <v>13</v>
       </c>
       <c r="E75" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <v>30104</v>
+        <v>30103</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C76" s="4">
-        <v>376</v>
+        <v>2345</v>
       </c>
       <c r="D76" s="3">
         <v>13</v>
       </c>
       <c r="E76" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -2008,410 +2008,443 @@
         <v>30104</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C77" s="4">
-        <v>7767</v>
+        <v>176</v>
       </c>
       <c r="D77" s="3">
         <v>13</v>
       </c>
       <c r="E77" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <v>30105</v>
+        <v>30104</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C78" s="4">
-        <v>3548</v>
+        <v>7767</v>
       </c>
       <c r="D78" s="3">
         <v>13</v>
       </c>
       <c r="E78" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
-        <v>30106</v>
+        <v>30105</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C79" s="4">
-        <v>3875</v>
+        <v>3548</v>
       </c>
       <c r="D79" s="3">
         <v>13</v>
       </c>
       <c r="E79" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <v>30107</v>
+        <v>30106</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C80" s="4">
-        <v>1037</v>
+        <v>3875</v>
       </c>
       <c r="D80" s="3">
         <v>13</v>
       </c>
       <c r="E80" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <v>30108</v>
+        <v>30107</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C81" s="4">
-        <v>120</v>
+        <v>1037</v>
       </c>
       <c r="D81" s="3">
         <v>13</v>
       </c>
       <c r="E81" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
-        <v>30108</v>
+        <v>30107</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C82" s="4">
-        <v>3904</v>
+        <v>10128</v>
       </c>
       <c r="D82" s="3">
         <v>13</v>
       </c>
       <c r="E82" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
-        <v>30109</v>
+        <v>30108</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C83" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D83" s="3">
         <v>13</v>
       </c>
       <c r="E83" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
-        <v>30109</v>
+        <v>30108</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C84" s="4">
-        <v>5932</v>
+        <v>3904</v>
       </c>
       <c r="D84" s="3">
         <v>13</v>
       </c>
       <c r="E84" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
-        <v>30110</v>
+        <v>30109</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C85" s="4">
-        <v>2687</v>
+        <v>90</v>
       </c>
       <c r="D85" s="3">
         <v>13</v>
       </c>
       <c r="E85" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
-        <v>30110</v>
+        <v>30109</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C86" s="4">
-        <v>3540</v>
+        <v>5932</v>
       </c>
       <c r="D86" s="3">
         <v>13</v>
       </c>
       <c r="E86" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
-        <v>30111</v>
+        <v>30110</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C87" s="4">
-        <v>2370</v>
+        <v>2647</v>
       </c>
       <c r="D87" s="3">
         <v>13</v>
       </c>
       <c r="E87" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
-        <v>30111</v>
+        <v>30110</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C88" s="4">
-        <v>7781</v>
+        <v>3540</v>
       </c>
       <c r="D88" s="3">
         <v>13</v>
       </c>
       <c r="E88" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <v>30113</v>
+        <v>30111</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C89" s="4">
-        <v>830</v>
+        <v>2370</v>
       </c>
       <c r="D89" s="3">
         <v>13</v>
       </c>
       <c r="E89" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <v>30113</v>
+        <v>30111</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C90" s="4">
-        <v>3381</v>
+        <v>7781</v>
       </c>
       <c r="D90" s="3">
         <v>13</v>
       </c>
       <c r="E90" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
-        <v>30117</v>
+        <v>30113</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C91" s="4">
-        <v>4951</v>
+        <v>830</v>
       </c>
       <c r="D91" s="3">
         <v>13</v>
       </c>
       <c r="E91" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
-        <v>30117</v>
+        <v>30113</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C92" s="4">
-        <v>9813</v>
+        <v>3381</v>
       </c>
       <c r="D92" s="3">
         <v>13</v>
       </c>
       <c r="E92" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
-        <v>30118</v>
+        <v>30114</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C93" s="4">
-        <v>2246</v>
+        <v>10103</v>
       </c>
       <c r="D93" s="3">
         <v>13</v>
       </c>
       <c r="E93" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
+        <v>30117</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C94" s="4">
+        <v>4951</v>
+      </c>
+      <c r="D94" s="3">
+        <v>13</v>
+      </c>
+      <c r="E94" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="3">
+        <v>30117</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C95" s="4">
+        <v>9773</v>
+      </c>
+      <c r="D95" s="3">
+        <v>13</v>
+      </c>
+      <c r="E95" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="3">
         <v>30118</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C94" s="4">
+      <c r="B96" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C96" s="4">
+        <v>2246</v>
+      </c>
+      <c r="D96" s="3">
+        <v>13</v>
+      </c>
+      <c r="E96" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="3">
+        <v>30118</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C97" s="4">
         <v>2840</v>
       </c>
-      <c r="D94" s="3">
-        <v>13</v>
-      </c>
-      <c r="E94" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="3"/>
-      <c r="B95" s="1"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="3"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="3"/>
-      <c r="B96" s="1"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="3"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="3"/>
-      <c r="B97" s="1"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="3"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D97" s="3">
+        <v>13</v>
+      </c>
+      <c r="E97" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="1"/>
       <c r="C98" s="4"/>
       <c r="D98" s="3"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="1"/>
       <c r="C99" s="4"/>
       <c r="D99" s="3"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="1"/>
       <c r="C100" s="4"/>
       <c r="D100" s="3"/>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="1"/>
       <c r="C101" s="4"/>
       <c r="D101" s="3"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
       <c r="B102" s="1"/>
       <c r="C102" s="4"/>
       <c r="D102" s="3"/>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
       <c r="B103" s="1"/>
       <c r="C103" s="4"/>
       <c r="D103" s="3"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
       <c r="B104" s="1"/>
       <c r="C104" s="4"/>
       <c r="D104" s="3"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
       <c r="B105" s="1"/>
       <c r="C105" s="4"/>
       <c r="D105" s="3"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="3"/>
       <c r="B106" s="1"/>
       <c r="C106" s="4"/>
       <c r="D106" s="3"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
       <c r="B107" s="1"/>
       <c r="C107" s="4"/>
       <c r="D107" s="3"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
       <c r="B108" s="1"/>
       <c r="C108" s="4"/>
       <c r="D108" s="3"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="3"/>
       <c r="B109" s="1"/>
       <c r="C109" s="4"/>
       <c r="D109" s="3"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="3"/>
       <c r="B110" s="1"/>
       <c r="C110" s="4"/>
       <c r="D110" s="3"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="1"/>
       <c r="C111" s="4"/>
       <c r="D111" s="3"/>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
       <c r="B112" s="1"/>
       <c r="C112" s="4"/>

--- a/data-source/ESTOQUEBASESLOCAL.xlsx
+++ b/data-source/ESTOQUEBASESLOCAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{623C5EE9-E726-4051-8B3C-7C3F13BD1A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F37833D-79CD-4EDE-A3E4-02BAB5E392B9}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{623C5EE9-E726-4051-8B3C-7C3F13BD1A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2CEFD6B-ACD1-4722-9C2E-092184DE3FCE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="1092" windowWidth="20736" windowHeight="11148" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha" sheetId="1" r:id="rId1"/>
@@ -379,6 +379,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
